--- a/data/ski_resort_database_seed.xlsx
+++ b/data/ski_resort_database_seed.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkiResorts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Notes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SkiResorts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE34"/>
+  <dimension ref="A1:AH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -719,6 +719,21 @@
           <t>Extended Data Note</t>
         </is>
       </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Coordinate Source</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="70" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -840,6 +855,17 @@
           <t>Flight access sourced from Israeli travel sites; snowfall/season estimated.</t>
         </is>
       </c>
+      <c r="AF5" t="n">
+        <v>41.8361</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>23.4874</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="70" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -961,6 +987,17 @@
           <t>Season dates sourced; snowfall estimated by regional comparison.</t>
         </is>
       </c>
+      <c r="AF6" t="n">
+        <v>45.9237</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>6.8693</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="70" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -1082,6 +1119,17 @@
           <t>TRANSFER CORRECTED (Aug 2026): Operators consistently state 196km / 3h-3h30 from Geneva (Alpine Fleet, Alps2Alps, Bens Bus). Sheet had 150km/2h30.</t>
         </is>
       </c>
+      <c r="AF7" t="n">
+        <v>45.2978</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>6.5838</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="70" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -1199,6 +1247,17 @@
         </is>
       </c>
       <c r="AE8" s="4" t="inlineStr"/>
+      <c r="AF8" t="n">
+        <v>47.1275</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>10.2637</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="70" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -1324,6 +1383,17 @@
           <t>TRANSFER CORRECTED (Aug 2026): Geneva rail route is 3h30-4h total per SBB routing; sheet had 2h40.</t>
         </is>
       </c>
+      <c r="AF9" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>7.7486</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="70" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1445,6 +1515,17 @@
           <t>Terrain park reputation sourced; snowfall/season estimated.</t>
         </is>
       </c>
+      <c r="AF10" t="n">
+        <v>46.5363</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>10.1335</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="70" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1570,6 +1651,17 @@
           <t>Season dates sourced; snowfall estimated.</t>
         </is>
       </c>
+      <c r="AF11" t="n">
+        <v>47.4464</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.3922</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="70" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -1691,6 +1783,17 @@
         </is>
       </c>
       <c r="AE12" s="4" t="inlineStr"/>
+      <c r="AF12" t="n">
+        <v>42.5769</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.6677</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="70" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -1816,6 +1919,17 @@
           <t>Snowfall and season dates sourced; terrain park estimated.</t>
         </is>
       </c>
+      <c r="AF13" t="n">
+        <v>45.9339</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>7.6318</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="70" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -1937,6 +2051,17 @@
         </is>
       </c>
       <c r="AE14" s="4" t="inlineStr"/>
+      <c r="AF14" t="n">
+        <v>46.5547</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11.7604</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="70" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -2062,6 +2187,17 @@
           <t>TRANSFER CORRECTED (Aug 2026): Operators quote ~2h30 from Geneva; sheet had 2h45 which overstated slightly.</t>
         </is>
       </c>
+      <c r="AF15" t="n">
+        <v>45.4154</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>6.6364</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="70" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -2183,6 +2319,17 @@
           <t>Snowfall sourced; season dates estimated.</t>
         </is>
       </c>
+      <c r="AF16" t="n">
+        <v>46.1002</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>7.2265</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="70" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -2304,6 +2451,17 @@
           <t>Published average-snowfall sources disagree substantially (236cm to 543cm depending on source) — this is a rough middle estimate, not a resolved figure. Season dates and flight access are solidly sourced.</t>
         </is>
       </c>
+      <c r="AF17" t="n">
+        <v>47.0126</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>10.2918</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="70" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -2425,6 +2583,17 @@
           <t>Glacier status and season dates sourced; snowfall estimated.</t>
         </is>
       </c>
+      <c r="AF18" t="n">
+        <v>46.9667</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="70" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -2546,6 +2715,17 @@
         </is>
       </c>
       <c r="AE19" s="4" t="inlineStr"/>
+      <c r="AF19" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="70" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -2667,6 +2847,17 @@
         </is>
       </c>
       <c r="AE20" s="4" t="inlineStr"/>
+      <c r="AF20" t="n">
+        <v>47.3914</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12.6364</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="70" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -2788,6 +2979,17 @@
         </is>
       </c>
       <c r="AE21" s="4" t="inlineStr"/>
+      <c r="AF21" t="n">
+        <v>45.0928</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>6.0699</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="70" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -2909,6 +3111,17 @@
         </is>
       </c>
       <c r="AE22" s="4" t="inlineStr"/>
+      <c r="AF22" t="n">
+        <v>41.6553</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>24.6935</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="70" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -3030,6 +3243,17 @@
         </is>
       </c>
       <c r="AE23" s="4" t="inlineStr"/>
+      <c r="AF23" t="n">
+        <v>45.597</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>25.5525</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="70" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -3151,6 +3375,17 @@
         </is>
       </c>
       <c r="AE24" s="4" t="inlineStr"/>
+      <c r="AF24" t="n">
+        <v>46.4569</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>13.7782</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="70" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -3272,6 +3507,17 @@
           <t>Season dates sourced; snowfall estimated by 3 Vallées regional comparison. | TRANSFER CORRECTED (Aug 2026): Operators quote 2h30 from Geneva; sheet had 2h15.</t>
         </is>
       </c>
+      <c r="AF25" t="n">
+        <v>45.415</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>6.565</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="70" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -3393,6 +3639,17 @@
           <t>Snowfall is an average of Val d'Isère (581cm) and Tignes (669cm) 10-year figures — the two sides differ. | TRANSFER CORRECTED (Aug 2026): Operators quote up to 2h45 from Geneva; sheet had 2h30.</t>
         </is>
       </c>
+      <c r="AF26" t="n">
+        <v>45.4737</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>6.9496</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API (midpoint of Val d'Isere + Tignes, lift-linked Espace Killy resorts)</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="70" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -3518,6 +3775,17 @@
           <t>Opening date and flight access sourced; snowfall/closing estimated.</t>
         </is>
       </c>
+      <c r="AF27" t="n">
+        <v>46.8667</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>11.0167</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="70" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -3643,6 +3911,17 @@
           <t>Season dates sourced; snowfall estimated.</t>
         </is>
       </c>
+      <c r="AF28" t="n">
+        <v>46.5369</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>12.139</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="70" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -3760,6 +4039,17 @@
         </is>
       </c>
       <c r="AE29" s="4" t="inlineStr"/>
+      <c r="AF29" t="n">
+        <v>45.0116</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>6.1255</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="70" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -3881,6 +4171,17 @@
         </is>
       </c>
       <c r="AE30" s="4" t="inlineStr"/>
+      <c r="AF30" t="n">
+        <v>42.7771</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>-0.3593</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="70" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -4002,6 +4303,17 @@
           <t>Season dates sourced; snowfall estimated.</t>
         </is>
       </c>
+      <c r="AF31" t="n">
+        <v>46.0066</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>6.6896</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="70" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -4123,6 +4435,17 @@
         </is>
       </c>
       <c r="AE32" s="4" t="inlineStr"/>
+      <c r="AF32" t="n">
+        <v>46.0415</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>13.7143</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="70" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -4244,6 +4567,17 @@
         </is>
       </c>
       <c r="AE33" s="4" t="inlineStr"/>
+      <c r="AF33" t="n">
+        <v>42.7878</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>-0.5288</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="70" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
@@ -4365,6 +4699,17 @@
         </is>
       </c>
       <c r="AE34" s="4" t="inlineStr"/>
+      <c r="AF34" t="n">
+        <v>45.0746</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>6.6989</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/ski_resort_database_seed.xlsx
+++ b/data/ski_resort_database_seed.xlsx
@@ -1695,17 +1695,17 @@
         <v>210</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>sourced</t>
         </is>
       </c>
       <c r="M12" s="6" t="n">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="AB12" s="4" t="inlineStr">
         <is>
-          <t>General/prior knowledge — flagged for dedicated web verification pass</t>
+          <t>grandvalira.com (via aggregated slope-count figures, accessed Aug 2026)</t>
         </is>
       </c>
       <c r="AC12" s="4" t="inlineStr">
         <is>
-          <t>Inferred from a qualitative description, not a published numeric breakdown.</t>
+          <t>142 total slopes: 23 green + 53 blue = 76 beginner-friendly, 46 red (intermediate), 20 black (advanced) -- count matches Grandvalira's own stated ~138-140 total slopes closely enough to trust the split.</t>
         </is>
       </c>
       <c r="AD12" s="4" t="inlineStr">
@@ -1830,14 +1830,14 @@
         <v>25</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>sourced</t>
         </is>
       </c>
       <c r="M13" s="5" t="n">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="AB13" s="4" t="inlineStr">
         <is>
-          <t>General/prior knowledge — flagged for dedicated web verification pass</t>
+          <t>aggregated piste-km stats for the Cervinia/Valtournenche sector (accessed Aug 2026)</t>
         </is>
       </c>
       <c r="AC13" s="4" t="inlineStr">
         <is>
-          <t>Inferred from a qualitative description, not a published numeric breakdown.</t>
+          <t>39km blue (incl. green), 107km red, 12km black of 158km -- consistent with the commonly-cited '~90% blue/red, small black minority' description of this resort found across multiple guides.</t>
         </is>
       </c>
       <c r="AD13" s="4" t="inlineStr">
@@ -2891,17 +2891,17 @@
         <v>250</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>sourced_conflicting</t>
         </is>
       </c>
       <c r="M21" s="4" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="AB21" s="4" t="inlineStr">
         <is>
-          <t>General/prior knowledge — flagged for dedicated web verification pass</t>
+          <t>skiworld.co.uk, snowstash.com, ultimatefrance.com (accessed Aug 2026)</t>
         </is>
       </c>
       <c r="AC21" s="4" t="inlineStr">
         <is>
-          <t>Inferred from a qualitative description, not a published numeric breakdown.</t>
+          <t>Published sources disagree by methodology, not just rounding: run-count-based breakdowns give ~63% beginner/23% intermediate/13% advanced (numerous short green/blue runs), while distance-based breakdowns of the resort's 250km give ~28% beginner/52% intermediate/20% advanced (red runs are much longer on average). This is a middle estimate, not a resolved figure.</t>
         </is>
       </c>
       <c r="AD21" s="4" t="inlineStr">
@@ -3023,17 +3023,17 @@
         <v>40</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>sourced_conflicting</t>
         </is>
       </c>
       <c r="M22" s="6" t="n">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="AB22" s="4" t="inlineStr">
         <is>
-          <t>General/prior knowledge — flagged for dedicated web verification pass</t>
+          <t>whatmegdidnext.com and an aggregated search summary (accessed Aug 2026)</t>
         </is>
       </c>
       <c r="AC22" s="4" t="inlineStr">
         <is>
-          <t>Inferred from a qualitative description, not a published numeric breakdown.</t>
+          <t>Two sources disagree: one states 50% beginner/37% intermediate/12% black of 37km, another 59%/25%/16%. Same general shape (majority easy terrain, small black portion) but real numeric disagreement. This is a middle estimate, not a resolved figure.</t>
         </is>
       </c>
       <c r="AD22" s="4" t="inlineStr">
@@ -3819,17 +3819,17 @@
         <v>120</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>estimated</t>
+          <t>sourced_conflicting</t>
         </is>
       </c>
       <c r="M28" s="5" t="n">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="AC28" s="4" t="inlineStr">
         <is>
-          <t>Inferred from a qualitative description, not a published numeric breakdown.</t>
+          <t>Published sources disagree substantially: one gives 33%/45%/16% beginner/intermediate/advanced, another ~33%/62%/5%, and a third (onthesnow.co.uk) uses a different intermediate/advanced/expert scheme with no beginner category at all. This is a middle estimate, not a resolved figure.</t>
         </is>
       </c>
       <c r="AD28" s="4" t="inlineStr">

--- a/data/ski_resort_database_seed.xlsx
+++ b/data/ski_resort_database_seed.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH34"/>
+  <dimension ref="A1:AH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4711,6 +4711,958 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Passo Tonale</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Pontedilegno-Tonale</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1883</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3088</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1205</v>
+      </c>
+      <c r="G35" t="n">
+        <v>27</v>
+      </c>
+      <c r="H35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" t="n">
+        <v>28</v>
+      </c>
+      <c r="J35" t="n">
+        <v>55</v>
+      </c>
+      <c r="K35" t="n">
+        <v>17</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>450</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Limited — Presena Glacier run</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>~14 Oct–mid Jun (glacier-extended; core season shorter)</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Indirect — via Bolzano/Milan Bergamo; no dedicated Israeli charter</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>2</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>5</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Bolzano (BZO) / Milan Bergamo (BGY)</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>65</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>~1h40 (Bolzano, est.)</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
+        <v>190</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>NEEDS VERIFICATION (not individually sourced this pass). Genuinely family-oriented -- pedestrian-friendly centre, ski-in-ski-out accommodation, easy slopes right from the resort. Presena Glacier gives snow-sure terrain at altitude for a resort with a relatively modest base.</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>skiclub.co.uk, j2ski.com, pontedilegnotonale.com (accessed Aug 2026)</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>28% blue/22 red/17% black per pontedilegnotonale.com's own published split (rounded to sum 100).</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>Season dates, piste km, lifts, terrain % and ski pass range sourced; snowfall, accommodation price and 1-5 ratings estimated. Snowfall ESTIMATED: only a single 'snowiest week' data point (43cm) was found, scaled to a plausible seasonal total by comparison to similar-altitude Alpine resorts already in this database -- not a direct annual citation.</t>
+        </is>
+      </c>
+      <c r="AF35" t="n">
+        <v>46.26073</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>10.58726</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Mayrhofen</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Zillertal Valley</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>630</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1870</v>
+      </c>
+      <c r="G36" t="n">
+        <v>45</v>
+      </c>
+      <c r="H36" t="n">
+        <v>142</v>
+      </c>
+      <c r="I36" t="n">
+        <v>30</v>
+      </c>
+      <c r="J36" t="n">
+        <v>49</v>
+      </c>
+      <c r="K36" t="n">
+        <v>21</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>219</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>No — nearest glacier (Hintertux) is a separate resort up-valley</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Early Dec–mid Apr</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Good — Innsbruck has direct scheduled flights (Israir) this season, ~1h away</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>3</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Innsbruck (INN)</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>75</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>~1h (est.)</t>
+        </is>
+      </c>
+      <c r="Y36" t="n">
+        <v>360</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>135</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>NEEDS VERIFICATION (not individually sourced this pass). Renowned specifically for long-running, high-volume apres-ski (arguably the standout nightlife resort in this database) -- a genuinely distinct positioning. Also has real steep terrain (Harakiri, Austria's steepest marked piste) despite a low, snow-marginal base elevation (630m).</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>j2ski.com, welove2ski.com, inthesnow.com (accessed Aug 2026)</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>30% blue/49% red/21% black per an aggregated piste-map summary (no separate green count found; likely folded into 'blue').</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>Terrain %, lifts, piste km, season and snowfall sourced; ski pass price, accommodation price and 1-5 ratings estimated.</t>
+        </is>
+      </c>
+      <c r="AF36" t="n">
+        <v>47.16667</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>11.86667</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Zell am See</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Zell am See-Kaprun</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>757</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3029</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2272</v>
+      </c>
+      <c r="G37" t="n">
+        <v>28</v>
+      </c>
+      <c r="H37" t="n">
+        <v>138</v>
+      </c>
+      <c r="I37" t="n">
+        <v>35</v>
+      </c>
+      <c r="J37" t="n">
+        <v>45</v>
+      </c>
+      <c r="K37" t="n">
+        <v>20</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>455</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Yes — Kitzsteinhorn glacier is part of the linked ski area</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Mid Oct–late May (glacier-extended)</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Good — Salzburg has had seasonal direct flights (Sun D'Or) in recent years</t>
+        </is>
+      </c>
+      <c r="R37" t="n">
+        <v>3</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Salzburg (SZG)</t>
+        </is>
+      </c>
+      <c r="W37" t="n">
+        <v>90</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>~1h15 (est.)</t>
+        </is>
+      </c>
+      <c r="Y37" t="n">
+        <v>370</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>140</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>NEEDS VERIFICATION (not individually sourced this pass). Two linked mountains on one pass -- Schmittenhoehe skews intermediate, Kaprun's Maiskogel has a dedicated nursery slope and wide, gentle terrain for families; glacier skiing at Kitzsteinhorn adds snow security most low/mid-elevation Austrian resorts lack. Free connecting ski bus between the two base towns.</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>j2ski.com, powderhounds.com, snowplaza.co.uk (accessed Aug 2026)</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>35% beginner/45% intermediate/20% advanced per an aggregated piste-map summary.</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>Terrain %, elevation, lifts, piste km, season and snowfall sourced; ski pass price, accommodation price and 1-5 ratings estimated.</t>
+        </is>
+      </c>
+      <c r="AF37" t="n">
+        <v>47.32306</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>12.79839</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Les Arcs</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Paradiski</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3226</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G38" t="n">
+        <v>82</v>
+      </c>
+      <c r="H38" t="n">
+        <v>200</v>
+      </c>
+      <c r="I38" t="n">
+        <v>10</v>
+      </c>
+      <c r="J38" t="n">
+        <v>42</v>
+      </c>
+      <c r="K38" t="n">
+        <v>48</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>500</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Mid Dec–late Apr</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Indirect — via Chambéry/Geneva; no dedicated Israeli charter</t>
+        </is>
+      </c>
+      <c r="R38" t="n">
+        <v>4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Chambéry (CMF)</t>
+        </is>
+      </c>
+      <c r="W38" t="n">
+        <v>127</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>~1h15-2h (sources vary 120-140km)</t>
+        </is>
+      </c>
+      <c r="Y38" t="n">
+        <v>368</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>NEEDS VERIFICATION (not individually sourced this pass). Cable-car linked to La Plagne (Paradiski, 425km combined) -- the steepest terrain skew of any resort in this database (48% advanced/expert). High-altitude and snow-secure (summit 3,226m); this is the same Paradiski link that made La Plagne itself come up in the same skideal.co.il research pass, though La Plagne isn't sold as its own package there.</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>wikipedia.org, j2ski.com, skibeat.co.uk, lesarcs-peiseyvallandry.com (accessed Aug 2026)</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>10% beginner/42% intermediate/34% advanced/14% expert per aggregated piste stats; advanced+expert folded together for this database's 3-way schema.</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>Elevation, lifts, piste km, terrain %, season and ski pass price sourced; snowfall, accommodation price and 1-5 ratings estimated. Airport distance has real source disagreement (120-140km). Snowfall ESTIMATED by comparison to Val Thorens (643cm, same general altitude band, already in this database) adjusted down for Les Arcs' lower base elevation -- no direct citation found.</t>
+        </is>
+      </c>
+      <c r="AF38" t="n">
+        <v>45.57755</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>6.78165</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Avoriaz</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Portes du Soleil</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2277</v>
+      </c>
+      <c r="F39" t="n">
+        <v>477</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34</v>
+      </c>
+      <c r="H39" t="n">
+        <v>75</v>
+      </c>
+      <c r="I39" t="n">
+        <v>66</v>
+      </c>
+      <c r="J39" t="n">
+        <v>23</v>
+      </c>
+      <c r="K39" t="n">
+        <v>11</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>500</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Mid Dec–mid Apr (typical for the region; not individually confirmed)</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Indirect — via Geneva; no dedicated Israeli charter</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>4</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Geneva (GVA)</t>
+        </is>
+      </c>
+      <c r="W39" t="n">
+        <v>90</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>~1h45 (sources vary 82-95km)</t>
+        </is>
+      </c>
+      <c r="Y39" t="n">
+        <v>320</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>140</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>NEEDS VERIFICATION (not individually sourced this pass). Entirely car-free, built ski-in-ski-out into the mountainside -- a genuinely distinct format from every other resort in this database. Gateway to Portes du Soleil (650km linked), one of the world's largest ski areas, and known for the legendary 'Swiss Wall' and real off-piste/freeride terrain (Lindarets powder fields) despite its family-resort reputation.</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>wikipedia.org, powderhounds.com, alps2alps.com (accessed Aug 2026)</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>7 green + 28 blue + 12 red + 6 black of 53 pistes in Avoriaz's own sector (count-based).</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>Elevation, lifts, piste km and terrain % sourced; ski pass price (Avoriaz has no standalone 6-day product), season end date, snowfall, accommodation price and 1-5 ratings estimated. 6-day ski pass price ESTIMATED: Avoriaz sells passes in 2-day increments, not a 6-day product, and by comparison to similarly-sized French linked areas already in this database. Snowfall ESTIMATED: only a single 'snowiest week' data point (47cm) was found, scaled to a plausible seasonal total -- not a direct annual citation.</t>
+        </is>
+      </c>
+      <c r="AF39" t="n">
+        <v>46.19243</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>6.77341</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Les Menuires</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Les Trois Vallées</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2850</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G40" t="n">
+        <v>30</v>
+      </c>
+      <c r="H40" t="n">
+        <v>160</v>
+      </c>
+      <c r="I40" t="n">
+        <v>61</v>
+      </c>
+      <c r="J40" t="n">
+        <v>32</v>
+      </c>
+      <c r="K40" t="n">
+        <v>8</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>450</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Early Dec–mid Apr</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Indirect — via Chambéry/Geneva; no dedicated Israeli charter</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Chambéry (CMF)</t>
+        </is>
+      </c>
+      <c r="W40" t="n">
+        <v>100</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>~1h45 (est.)</t>
+        </is>
+      </c>
+      <c r="Y40" t="n">
+        <v>315</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>NEEDS VERIFICATION (not individually sourced this pass). The value/budget base of Les 3 Vallées -- the same lift network already covered here via Courchevel, Méribel and Val Thorens, giving this database its first cheaper entry point into that circuit. 85% of terrain sits above 1,800m, genuinely snow-secure for its price tier.</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>powderhounds.com, j2ski.com, alps2alps.com (accessed Aug 2026)</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>12 green + 34 blue + 24 red + 6 black of 76 trails (count-based).</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>Elevation, lifts, piste km, terrain %, season and ski pass price sourced; snowfall, accommodation price and 1-5 ratings estimated. Snowfall ESTIMATED by comparison to Val Thorens (643cm, same Trois Vallées circuit, already in this database) adjusted down for Les Menuires' lower base elevation -- no direct citation found.</t>
+        </is>
+      </c>
+      <c r="AF40" t="n">
+        <v>45.32293</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>6.53757</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Vallnord (Pal-Arinsal)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Andorra</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Vallnord</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1550</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2560</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1010</v>
+      </c>
+      <c r="G41" t="n">
+        <v>29</v>
+      </c>
+      <c r="H41" t="n">
+        <v>63</v>
+      </c>
+      <c r="I41" t="n">
+        <v>52</v>
+      </c>
+      <c r="J41" t="n">
+        <v>27</v>
+      </c>
+      <c r="K41" t="n">
+        <v>21</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>378</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Early Dec–mid Apr</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Indirect only — via Barcelona/Toulouse with a long onward transfer; no dedicated Israeli charter</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>2</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>5</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Barcelona (BCN)</t>
+        </is>
+      </c>
+      <c r="W41" t="n">
+        <v>200</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>~2h45</t>
+        </is>
+      </c>
+      <c r="Y41" t="n">
+        <v>310</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>NEEDS VERIFICATION (not individually sourced this pass). Andorra's SMALLER, western-side ski area -- genuinely separate from this database's existing Grandvalira entry, not an alternate name for it (confirmed: different mountain, different valley). Explicitly positioned as the most family-oriented resort in the Pyrenees; more compact and relaxed than Grandvalira, gives Andorra a second, cheaper tier in this database.</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>maisonsport.com, arinsal.co.uk, j2ski.com, onthesnow.co.uk (accessed Aug 2026)</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>7 green + 16 blue + 12 red + 9 black of 44 runs (count-based).</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>Elevation, lifts, piste km, terrain %, season, snowfall and airport distance sourced (7-day pass price of EUR357 found, but no clean 6-day figure); accommodation price and 1-5 ratings estimated. 6-day ski pass price ESTIMATED by scaling down from a sourced 7-day adult price of EUR357 (snow-online.com) -- not a direct 6-day citation.</t>
+        </is>
+      </c>
+      <c r="AF41" t="n">
+        <v>42.54499</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.51483</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:AE2"/>

--- a/data/ski_resort_database_seed.xlsx
+++ b/data/ski_resort_database_seed.xlsx
@@ -563,6 +563,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5201,7 +5202,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Chambéry (CMF)</t>
+          <t>Chambéry (CMF) / Geneva (GVA)</t>
         </is>
       </c>
       <c r="W38" t="n">
@@ -5209,7 +5210,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>~1h15-2h (sources vary 120-140km)</t>
+          <t>~1h15-2h (CMF, sources vary 120-140km) / 3h20 (GVA)</t>
         </is>
       </c>
       <c r="Y38" t="n">
@@ -5473,7 +5474,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Chambéry (CMF)</t>
+          <t>Chambéry (CMF) / Geneva (GVA)</t>
         </is>
       </c>
       <c r="W40" t="n">
@@ -5481,7 +5482,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>~1h45 (est.)</t>
+          <t>~1h45 (CMF, est.) / 3h30 (GVA)</t>
         </is>
       </c>
       <c r="Y40" t="n">

--- a/data/ski_resort_database_seed.xlsx
+++ b/data/ski_resort_database_seed.xlsx
@@ -1610,7 +1610,7 @@
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>Innsbruck (INN) / Salzburg (SZG)</t>
+          <t>Innsbruck (INN) / Salzburg (SZG) / Munich (MUC)</t>
         </is>
       </c>
       <c r="W11" s="4" t="n">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="X11" s="4" t="inlineStr">
         <is>
-          <t>~1h-1h30 (est.)</t>
+          <t>~1h-1h30 (INN, est.) / ~1h-1h30 (SZG, est.) / 3h20 (MUC)</t>
         </is>
       </c>
       <c r="Y11" s="4" t="n">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>Innsbruck (INN)</t>
+          <t>Innsbruck (INN) / Munich (MUC)</t>
         </is>
       </c>
       <c r="W17" s="4" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="X17" s="4" t="inlineStr">
         <is>
-          <t>1h30</t>
+          <t>1h30 (INN) / 4h (MUC)</t>
         </is>
       </c>
       <c r="Y17" s="4" t="n">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>Innsbruck (INN)</t>
+          <t>Innsbruck (INN) / Munich (MUC)</t>
         </is>
       </c>
       <c r="W18" s="4" t="n">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="X18" s="4" t="inlineStr">
         <is>
-          <t>1h15-1h30</t>
+          <t>1h15-1h30 (INN) / 3h50 (MUC)</t>
         </is>
       </c>
       <c r="Y18" s="4" t="n">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>Salzburg (SZG)</t>
+          <t>Salzburg (SZG) / Munich (MUC)</t>
         </is>
       </c>
       <c r="W20" s="4" t="n">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="X20" s="4" t="inlineStr">
         <is>
-          <t>~1h (est.)</t>
+          <t>~1h (SZG, est.) / 3h30 (MUC)</t>
         </is>
       </c>
       <c r="Y20" s="4" t="n">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>Ljubljana (LJU)</t>
+          <t>Ljubljana (LJU) / Venice Marco Polo (VCE)</t>
         </is>
       </c>
       <c r="W24" s="4" t="n">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="X24" s="4" t="inlineStr">
         <is>
-          <t>~1h15 (est.)</t>
+          <t>~1h15 (LJU, est.) / 2h20 (VCE)</t>
         </is>
       </c>
       <c r="Y24" s="4" t="n">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>Ljubljana (LJU)</t>
+          <t>Ljubljana (LJU) / Venice Marco Polo (VCE)</t>
         </is>
       </c>
       <c r="W32" s="4" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="X32" s="4" t="inlineStr">
         <is>
-          <t>~20min (closest airport-to-resort in this database, est.)</t>
+          <t>~20min (LJU, closest airport-to-resort in this database, est.) / ~2h45 (VCE, est.)</t>
         </is>
       </c>
       <c r="Y32" s="4" t="n">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Bolzano (BZO) / Milan Bergamo (BGY)</t>
+          <t>Bolzano (BZO) / Milan Bergamo (BGY) / Verona (VRN)</t>
         </is>
       </c>
       <c r="W35" t="n">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>~1h40 (Bolzano, est.)</t>
+          <t>~1h40 (BZO, est.) / 2h15 (VRN)</t>
         </is>
       </c>
       <c r="Y35" t="n">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Innsbruck (INN)</t>
+          <t>Innsbruck (INN) / Munich (MUC)</t>
         </is>
       </c>
       <c r="W36" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>~1h (est.)</t>
+          <t>~1h (INN, est.) / 2h45 (MUC)</t>
         </is>
       </c>
       <c r="Y36" t="n">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Salzburg (SZG)</t>
+          <t>Salzburg (SZG) / Munich (MUC)</t>
         </is>
       </c>
       <c r="W37" t="n">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>~1h15 (est.)</t>
+          <t>~1h15 (SZG, est.) / 3h30 (MUC)</t>
         </is>
       </c>
       <c r="Y37" t="n">

--- a/data/ski_resort_database_seed.xlsx
+++ b/data/ski_resort_database_seed.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH41"/>
+  <dimension ref="A1:AH43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5661,6 +5660,268 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gudauri</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Greater Caucasus (Kazbegi)</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1990</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3279</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1289</v>
+      </c>
+      <c r="G42" t="n">
+        <v>20</v>
+      </c>
+      <c r="H42" t="n">
+        <v>76</v>
+      </c>
+      <c r="I42" t="n">
+        <v>30</v>
+      </c>
+      <c r="J42" t="n">
+        <v>50</v>
+      </c>
+      <c r="K42" t="n">
+        <v>20</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>350</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>~late Dec–mid Apr (high-altitude, opens ~Dec 27)</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Excellent — Tbilisi (TBS) has direct scheduled TLV service year-round (probed live 2026-08-28: EUR400 Oct / EUR766 Jan round trips priced on Google Flights); one of the largest Israeli ski markets outside Europe</t>
+        </is>
+      </c>
+      <c r="R42" t="n">
+        <v>5</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Tbilisi (TBS)</t>
+        </is>
+      </c>
+      <c r="W42" t="n">
+        <v>120</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>2h (TBS)</t>
+        </is>
+      </c>
+      <c r="Y42" t="n">
+        <v>116</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Highest-value freeride destination in the database: entirely above the tree line, 1,990-3,279m, famous for accessible off-piste and heliskiing; modern Doppelmayr lifts; nightlife modest, resort is purpose-built. 6-day pass 340 GEL (~EUR116). Accommodation figure estimated.</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>skiresort.com, gudauri.com, snow-forecast.com, j2ski.com (accessed Aug 2026)</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>Terrain split estimated from qualitative guides; pass converted from GEL.</t>
+        </is>
+      </c>
+      <c r="AF42" t="n">
+        <v>42.4796</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>44.4805</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sella Ronda (Dolomiti)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sella Ronda / Dolomiti Superski</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1465</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3269</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1804</v>
+      </c>
+      <c r="G43" t="n">
+        <v>450</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I43" t="n">
+        <v>30</v>
+      </c>
+      <c r="J43" t="n">
+        <v>55</v>
+      </c>
+      <c r="K43" t="n">
+        <v>15</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>300</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Yes (Marmolada)</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>~4 Dec–4 Apr (published 26/27 dates)</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Indirect — via Innsbruck/Verona/Venice; INN and VRN both have priced TLV service (probed live 2026-08-28)</t>
+        </is>
+      </c>
+      <c r="R43" t="n">
+        <v>3</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>5</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Verona (VRN) / Innsbruck (INN) / Venice Marco Polo (VCE)</t>
+        </is>
+      </c>
+      <c r="W43" t="n">
+        <v>180</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>~2h30 (VRN, est.) / ~2h (INN, est.) / ~2h45 (VCE, est.)</t>
+        </is>
+      </c>
+      <c r="Y43" t="n">
+        <v>357</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>AREA SCOPE, like Grandvalira: the 44km Sella Ronda circuit (23km skied) around the Sella massif linking Selva, Corvara/Colfosco, Arabba and Canazei -- lift/piste figures are the full Dolomiti Superski network (450 lifts / 1,200km) its one pass covers. Overlaps Val Gardena (Selva), which is also in this database as the single-valley entry; this row is the circuit-as-destination the Israeli operators sell. 6-day Dolomiti Superski EUR357 (25/26 published price; 26/27 not yet out).</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>dolomitisuperski.com, val-gardena.com, alta-badia.org, dolomiti.org (accessed Aug 2026)</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>Terrain split estimated; area-scope figures per the note.</t>
+        </is>
+      </c>
+      <c r="AF43" t="n">
+        <v>46.509</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>11.803</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API (Passo Gardena area midpoint)</t>
         </is>
       </c>
     </row>

--- a/data/ski_resort_database_seed.xlsx
+++ b/data/ski_resort_database_seed.xlsx
@@ -563,6 +563,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -821,11 +822,11 @@
         </is>
       </c>
       <c r="W5" s="4" t="n">
-        <v>160</v>
+        <v>159.5</v>
       </c>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t>2h-2h30</t>
+          <t>2h05 (SOF)</t>
         </is>
       </c>
       <c r="Y5" s="4" t="n">
@@ -957,7 +958,7 @@
       </c>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>1h-1h15</t>
+          <t>1h09 (GVA)</t>
         </is>
       </c>
       <c r="Y6" s="4" t="n">
@@ -1085,11 +1086,11 @@
         </is>
       </c>
       <c r="W7" s="4" t="n">
-        <v>196</v>
+        <v>155.2</v>
       </c>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>3h (GVA) / 1h45 (CMF)</t>
+          <t>2h31 (GVA) / 1h48 (CMF)</t>
         </is>
       </c>
       <c r="Y7" s="4" t="n">
@@ -1217,11 +1218,11 @@
         </is>
       </c>
       <c r="W8" s="4" t="n">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>1h-1h30</t>
+          <t>1h13 (INN)</t>
         </is>
       </c>
       <c r="Y8" s="4" t="n">
@@ -1345,11 +1346,11 @@
         </is>
       </c>
       <c r="W9" s="4" t="n">
-        <v>231</v>
+        <v>229.5</v>
       </c>
       <c r="X9" s="4" t="inlineStr">
         <is>
-          <t>3h30 (GVA, incl. Tasch rail leg) / 3h (MXP)</t>
+          <t>2h40 (GVA) / 2h42 (MXP)</t>
         </is>
       </c>
       <c r="Y9" s="4" t="n">
@@ -1481,11 +1482,11 @@
         </is>
       </c>
       <c r="W10" s="4" t="n">
-        <v>200</v>
+        <v>178.1</v>
       </c>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>3h30-4h</t>
+          <t>3h22 (BGY) / 2h44 (INN)</t>
         </is>
       </c>
       <c r="Y10" s="4" t="n">
@@ -1613,11 +1614,11 @@
         </is>
       </c>
       <c r="W11" s="4" t="n">
-        <v>90</v>
+        <v>97.8</v>
       </c>
       <c r="X11" s="4" t="inlineStr">
         <is>
-          <t>~1h-1h30 (INN, est.) / ~1h-1h30 (SZG, est.) / 3h20 (MUC)</t>
+          <t>1h25 (INN) / 1h13 (SZG) / 1h57 (MUC)</t>
         </is>
       </c>
       <c r="Y11" s="4" t="n">
@@ -1749,11 +1750,11 @@
         </is>
       </c>
       <c r="W12" s="4" t="n">
-        <v>220</v>
+        <v>208.8</v>
       </c>
       <c r="X12" s="4" t="inlineStr">
         <is>
-          <t>~3h (BCN, est.)</t>
+          <t>2h47 (BCN) / 2h28 (TLS)</t>
         </is>
       </c>
       <c r="Y12" s="4" t="n">
@@ -1881,11 +1882,11 @@
         </is>
       </c>
       <c r="W13" s="4" t="n">
-        <v>160</v>
+        <v>182.6</v>
       </c>
       <c r="X13" s="4" t="inlineStr">
         <is>
-          <t>~2h30-3h (est.)</t>
+          <t>2h17 (MXP)</t>
         </is>
       </c>
       <c r="Y13" s="4" t="n">
@@ -2017,11 +2018,11 @@
         </is>
       </c>
       <c r="W14" s="4" t="n">
-        <v>100</v>
+        <v>119.9</v>
       </c>
       <c r="X14" s="4" t="inlineStr">
         <is>
-          <t>~1h30 (INN, est.)</t>
+          <t>1h54 (INN) / 57min (BZO) / 2h21 (VRN)</t>
         </is>
       </c>
       <c r="Y14" s="4" t="n">
@@ -2145,15 +2146,15 @@
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>Chambéry (CMF) / Geneva (GVA)</t>
+          <t>Geneva (GVA) / Chambéry (CMF)</t>
         </is>
       </c>
       <c r="W15" s="4" t="n">
-        <v>110</v>
+        <v>134.7</v>
       </c>
       <c r="X15" s="4" t="inlineStr">
         <is>
-          <t>2h30 (GVA) / 1h45 (CMF)</t>
+          <t>2h08 (GVA) / 1h25 (CMF)</t>
         </is>
       </c>
       <c r="Y15" s="4" t="n">
@@ -2285,11 +2286,11 @@
         </is>
       </c>
       <c r="W16" s="4" t="n">
-        <v>160</v>
+        <v>160.4</v>
       </c>
       <c r="X16" s="4" t="inlineStr">
         <is>
-          <t>2h-2h30</t>
+          <t>1h53 (GVA)</t>
         </is>
       </c>
       <c r="Y16" s="4" t="n">
@@ -2417,11 +2418,11 @@
         </is>
       </c>
       <c r="W17" s="4" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="X17" s="4" t="inlineStr">
         <is>
-          <t>1h30 (INN) / 4h (MUC)</t>
+          <t>1h21 (INN) / 3h15 (MUC)</t>
         </is>
       </c>
       <c r="Y17" s="4" t="n">
@@ -2549,11 +2550,11 @@
         </is>
       </c>
       <c r="W18" s="4" t="n">
-        <v>83</v>
+        <v>97.5</v>
       </c>
       <c r="X18" s="4" t="inlineStr">
         <is>
-          <t>1h15-1h30 (INN) / 3h50 (MUC)</t>
+          <t>1h33 (INN) / 3h32 (MUC)</t>
         </is>
       </c>
       <c r="Y18" s="4" t="n">
@@ -2681,11 +2682,11 @@
         </is>
       </c>
       <c r="W19" s="4" t="n">
-        <v>150</v>
+        <v>136.4</v>
       </c>
       <c r="X19" s="4" t="inlineStr">
         <is>
-          <t>~2h (est.)</t>
+          <t>2h22 (TRN) / 3h00 (GNB)</t>
         </is>
       </c>
       <c r="Y19" s="4" t="n">
@@ -2813,11 +2814,11 @@
         </is>
       </c>
       <c r="W20" s="4" t="n">
-        <v>75</v>
+        <v>86.5</v>
       </c>
       <c r="X20" s="4" t="inlineStr">
         <is>
-          <t>~1h (SZG, est.) / 3h30 (MUC)</t>
+          <t>1h25 (SZG) / 2h46 (MUC)</t>
         </is>
       </c>
       <c r="Y20" s="4" t="n">
@@ -2941,15 +2942,15 @@
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>Grenoble (GNB) / Lyon (LYS)</t>
+          <t>Lyon (LYS) / Grenoble (GNB)</t>
         </is>
       </c>
       <c r="W21" s="4" t="n">
-        <v>65</v>
+        <v>153.7</v>
       </c>
       <c r="X21" s="4" t="inlineStr">
         <is>
-          <t>~1h15 (GNB, est.)</t>
+          <t>1h59 (LYS) / 1h33 (GNB)</t>
         </is>
       </c>
       <c r="Y21" s="4" t="n">
@@ -3073,15 +3074,15 @@
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>Plovdiv (PDV) / Sofia (SOF)</t>
+          <t>Sofia (SOF) / Plovdiv (PDV)</t>
         </is>
       </c>
       <c r="W22" s="4" t="n">
-        <v>90</v>
+        <v>225.2</v>
       </c>
       <c r="X22" s="4" t="inlineStr">
         <is>
-          <t>~1h30 (PDV, est.)</t>
+          <t>3h00 (SOF) / 1h29 (PDV)</t>
         </is>
       </c>
       <c r="Y22" s="4" t="n">
@@ -3209,11 +3210,11 @@
         </is>
       </c>
       <c r="W23" s="4" t="n">
-        <v>170</v>
+        <v>156.6</v>
       </c>
       <c r="X23" s="4" t="inlineStr">
         <is>
-          <t>~2h30 (OTP, est.)</t>
+          <t>2h27 (OTP)</t>
         </is>
       </c>
       <c r="Y23" s="4" t="n">
@@ -3341,11 +3342,11 @@
         </is>
       </c>
       <c r="W24" s="4" t="n">
-        <v>90</v>
+        <v>63.7</v>
       </c>
       <c r="X24" s="4" t="inlineStr">
         <is>
-          <t>~1h15 (LJU, est.) / 2h20 (VCE)</t>
+          <t>50min (LJU) / 2h32 (VCE)</t>
         </is>
       </c>
       <c r="Y24" s="4" t="n">
@@ -3469,15 +3470,15 @@
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>Chambéry (CMF) / Geneva (GVA)</t>
+          <t>Geneva (GVA) / Chambéry (CMF)</t>
         </is>
       </c>
       <c r="W25" s="4" t="n">
-        <v>100</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="X25" s="4" t="inlineStr">
         <is>
-          <t>2h30 (GVA) / 1h45 (CMF)</t>
+          <t>55min (GVA) / 1h17 (CMF)</t>
         </is>
       </c>
       <c r="Y25" s="4" t="n">
@@ -3601,15 +3602,15 @@
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>Chambéry (CMF) / Geneva (GVA) / Lyon (LYS)</t>
+          <t>Geneva (GVA) / Lyon (LYS) / Chambéry (CMF)</t>
         </is>
       </c>
       <c r="W26" s="4" t="n">
-        <v>145</v>
+        <v>177.6</v>
       </c>
       <c r="X26" s="4" t="inlineStr">
         <is>
-          <t>2h45 (GVA) / 1h45 (CMF)</t>
+          <t>2h52 (GVA) / 2h54 (LYS) / 2h10 (CMF)</t>
         </is>
       </c>
       <c r="Y26" s="4" t="n">
@@ -3737,11 +3738,11 @@
         </is>
       </c>
       <c r="W27" s="4" t="n">
-        <v>97</v>
+        <v>99.2</v>
       </c>
       <c r="X27" s="4" t="inlineStr">
         <is>
-          <t>1h40</t>
+          <t>1h34 (INN)</t>
         </is>
       </c>
       <c r="Y27" s="4" t="n">
@@ -3873,11 +3874,11 @@
         </is>
       </c>
       <c r="W28" s="4" t="n">
-        <v>148</v>
+        <v>147.5</v>
       </c>
       <c r="X28" s="4" t="inlineStr">
         <is>
-          <t>1h50 (VCE) / 2h10 (INN)</t>
+          <t>1h55 (VCE) / 2h39 (INN)</t>
         </is>
       </c>
       <c r="Y28" s="4" t="n">
@@ -4005,15 +4006,15 @@
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>Grenoble (GNB) / Lyon (LYS)</t>
+          <t>Lyon (LYS) / Grenoble (GNB)</t>
         </is>
       </c>
       <c r="W29" s="4" t="n">
-        <v>75</v>
+        <v>167.2</v>
       </c>
       <c r="X29" s="4" t="inlineStr">
         <is>
-          <t>~1h30 (GNB, est.)</t>
+          <t>2h19 (LYS) / 1h53 (GNB)</t>
         </is>
       </c>
       <c r="Y29" s="4" t="n">
@@ -4133,15 +4134,15 @@
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>Zaragoza (ZAZ) / Lourdes (LDE, France)</t>
+          <t>Barcelona (BCN) / Zaragoza (ZAZ)</t>
         </is>
       </c>
       <c r="W30" s="4" t="n">
-        <v>170</v>
+        <v>352.7</v>
       </c>
       <c r="X30" s="4" t="inlineStr">
         <is>
-          <t>~2h (ZAZ, est.)</t>
+          <t>3h47 (BCN) / 2h01 (ZAZ)</t>
         </is>
       </c>
       <c r="Y30" s="4" t="n">
@@ -4269,11 +4270,11 @@
         </is>
       </c>
       <c r="W31" s="4" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="X31" s="4" t="inlineStr">
         <is>
-          <t>~1h (est.)</t>
+          <t>1h17 (GVA)</t>
         </is>
       </c>
       <c r="Y31" s="4" t="n">
@@ -4401,11 +4402,11 @@
         </is>
       </c>
       <c r="W32" s="4" t="n">
-        <v>10</v>
+        <v>22.6</v>
       </c>
       <c r="X32" s="4" t="inlineStr">
         <is>
-          <t>~20min (LJU, closest airport-to-resort in this database, est.) / ~2h45 (VCE, est.)</t>
+          <t>42min (LJU) / 3h16 (VCE)</t>
         </is>
       </c>
       <c r="Y32" s="4" t="n">
@@ -4529,15 +4530,15 @@
       </c>
       <c r="V33" s="4" t="inlineStr">
         <is>
-          <t>Zaragoza (ZAZ) / Pau (PUF, France)</t>
+          <t>Barcelona (BCN) / Zaragoza (ZAZ)</t>
         </is>
       </c>
       <c r="W33" s="4" t="n">
-        <v>160</v>
+        <v>362.5</v>
       </c>
       <c r="X33" s="4" t="inlineStr">
         <is>
-          <t>~2h (est.)</t>
+          <t>3h49 (BCN) / 2h03 (ZAZ)</t>
         </is>
       </c>
       <c r="Y33" s="4" t="n">
@@ -4665,11 +4666,11 @@
         </is>
       </c>
       <c r="W34" s="4" t="n">
-        <v>90</v>
+        <v>102.8</v>
       </c>
       <c r="X34" s="4" t="inlineStr">
         <is>
-          <t>~1h15 (est.)</t>
+          <t>1h17 (TRN)</t>
         </is>
       </c>
       <c r="Y34" s="4" t="n">
@@ -4793,15 +4794,15 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Bolzano (BZO) / Milan Bergamo (BGY) / Verona (VRN)</t>
+          <t>Milan Bergamo (BGY) / Verona (VRN) / Bolzano (BZO)</t>
         </is>
       </c>
       <c r="W35" t="n">
-        <v>65</v>
+        <v>127.3</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>~1h40 (BZO, est.) / 2h15 (VRN)</t>
+          <t>2h12 (BGY) / 2h29 (VRN) / 1h51 (BZO)</t>
         </is>
       </c>
       <c r="Y35" t="n">
@@ -4933,11 +4934,11 @@
         </is>
       </c>
       <c r="W36" t="n">
-        <v>75</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>~1h (INN, est.) / 2h45 (MUC)</t>
+          <t>1h05 (INN) / 2h14 (MUC)</t>
         </is>
       </c>
       <c r="Y36" t="n">
@@ -5069,11 +5070,11 @@
         </is>
       </c>
       <c r="W37" t="n">
-        <v>90</v>
+        <v>76.5</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>~1h15 (SZG, est.) / 3h30 (MUC)</t>
+          <t>1h16 (SZG) / 2h37 (MUC)</t>
         </is>
       </c>
       <c r="Y37" t="n">
@@ -5201,15 +5202,15 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Chambéry (CMF) / Geneva (GVA)</t>
+          <t>Geneva (GVA) / Chambéry (CMF)</t>
         </is>
       </c>
       <c r="W38" t="n">
-        <v>127</v>
+        <v>159.6</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>~1h15-2h (CMF, sources vary 120-140km) / 3h20 (GVA)</t>
+          <t>2h33 (GVA) / 1h50 (CMF)</t>
         </is>
       </c>
       <c r="Y38" t="n">
@@ -5341,11 +5342,11 @@
         </is>
       </c>
       <c r="W39" t="n">
-        <v>90</v>
+        <v>102.5</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>~1h45 (sources vary 82-95km)</t>
+          <t>1h39 (GVA)</t>
         </is>
       </c>
       <c r="Y39" t="n">
@@ -5473,15 +5474,15 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Chambéry (CMF) / Geneva (GVA)</t>
+          <t>Geneva (GVA) / Chambéry (CMF)</t>
         </is>
       </c>
       <c r="W40" t="n">
-        <v>100</v>
+        <v>145.6</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>~1h45 (CMF, est.) / 3h30 (GVA)</t>
+          <t>2h19 (GVA) / 1h36 (CMF)</t>
         </is>
       </c>
       <c r="Y40" t="n">
@@ -5613,11 +5614,11 @@
         </is>
       </c>
       <c r="W41" t="n">
-        <v>200</v>
+        <v>215.8</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>~2h45</t>
+          <t>2h52 (BCN)</t>
         </is>
       </c>
       <c r="Y41" t="n">
@@ -5749,11 +5750,11 @@
         </is>
       </c>
       <c r="W42" t="n">
-        <v>120</v>
+        <v>136.5</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2h (TBS)</t>
+          <t>2h35 (TBS)</t>
         </is>
       </c>
       <c r="Y42" t="n">
@@ -5880,11 +5881,11 @@
         </is>
       </c>
       <c r="W43" t="n">
-        <v>180</v>
+        <v>193.4</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>~2h30 (VRN, est.) / ~2h (INN, est.) / ~2h45 (VCE, est.)</t>
+          <t>2h34 (VRN) / 2h53 (INN) / 2h15 (VCE)</t>
         </is>
       </c>
       <c r="Y43" t="n">

--- a/data/ski_resort_database_seed.xlsx
+++ b/data/ski_resort_database_seed.xlsx
@@ -1878,7 +1878,7 @@
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>Milan Malpensa (MXP)</t>
+          <t>Milan Malpensa (MXP) / Turin (TRN)</t>
         </is>
       </c>
       <c r="W13" s="4" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="X13" s="4" t="inlineStr">
         <is>
-          <t>2h17 (MXP)</t>
+          <t>2h17 (MXP) / 1h39 (TRN)</t>
         </is>
       </c>
       <c r="Y13" s="4" t="n">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>Bucharest (OTP) / Brasov (BRV, seasonal)</t>
+          <t>Bucharest (OTP) / Brasov (GHV)</t>
         </is>
       </c>
       <c r="W23" s="4" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="X23" s="4" t="inlineStr">
         <is>
-          <t>2h27 (OTP)</t>
+          <t>2h27 (OTP) / 31min (GHV)</t>
         </is>
       </c>
       <c r="Y23" s="4" t="n">
@@ -4437,14 +4437,14 @@
       </c>
       <c r="AE32" s="4" t="inlineStr"/>
       <c r="AF32" t="n">
-        <v>46.0415</v>
+        <v>46.2972</v>
       </c>
       <c r="AG32" t="n">
-        <v>13.7143</v>
+        <v>14.5325</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Open-Meteo geocoding API</t>
+          <t>corrected by hand 2026-08-29 (geocoder had placed it 69km west)</t>
         </is>
       </c>
     </row>

--- a/data/ski_resort_database_seed.xlsx
+++ b/data/ski_resort_database_seed.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH43"/>
+  <dimension ref="A1:AH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1214,7 +1213,7 @@
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>Innsbruck (INN)</t>
+          <t>Innsbruck (INN) / Munich (MUC)</t>
         </is>
       </c>
       <c r="W8" s="4" t="n">
@@ -1222,7 +1221,7 @@
       </c>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>1h13 (INN)</t>
+          <t>1h13 (INN) / 3h07 (MUC)</t>
         </is>
       </c>
       <c r="Y8" s="4" t="n">
@@ -1361,7 +1360,7 @@
       </c>
       <c r="AA9" s="4" t="inlineStr">
         <is>
-          <t>Iconic, year-round glacier skiing, very snow-sure; car-free village (final leg by train from Täsch); premium/luxury price point; can ski across to Cervinia in Italy on the international pass — good for a 2-country day.</t>
+          <t>CAR-FREE RESORT — road transfers terminate at Täsch and travellers must change to the shuttle train for the final leg. Any Alps2Alps or Omio quote to 'Zermatt' is really a quote to Täsch, so both journey time and cost are understated until that leg is modelled. Year-round glacier skiing, 5/5 snow reliability, lift-linked to Cervinia.</t>
         </is>
       </c>
       <c r="AB9" s="4" t="inlineStr">
@@ -1478,15 +1477,15 @@
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>Milan (MXP/LIN) / Bergamo (BGY) / Innsbruck (INN)</t>
+          <t>Milan Malpensa (MXP) / Innsbruck (INN)</t>
         </is>
       </c>
       <c r="W10" s="4" t="n">
-        <v>178.1</v>
+        <v>225.2</v>
       </c>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>3h22 (BGY) / 2h44 (INN)</t>
+          <t>3h34 (MXP) / 2h44 (INN)</t>
         </is>
       </c>
       <c r="Y10" s="4" t="n">
@@ -1746,15 +1745,15 @@
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>Barcelona (BCN) / Toulouse (TLS)</t>
+          <t>Toulouse (TLS) / Barcelona (BCN)</t>
         </is>
       </c>
       <c r="W12" s="4" t="n">
-        <v>208.8</v>
+        <v>179.4</v>
       </c>
       <c r="X12" s="4" t="inlineStr">
         <is>
-          <t>2h47 (BCN) / 2h28 (TLS)</t>
+          <t>2h28 (TLS) / 2h47 (BCN)</t>
         </is>
       </c>
       <c r="Y12" s="4" t="n">
@@ -1882,11 +1881,11 @@
         </is>
       </c>
       <c r="W13" s="4" t="n">
-        <v>182.6</v>
+        <v>183.1</v>
       </c>
       <c r="X13" s="4" t="inlineStr">
         <is>
-          <t>2h17 (MXP) / 1h39 (TRN)</t>
+          <t>2h16 (MXP) / 1h39 (TRN)</t>
         </is>
       </c>
       <c r="Y13" s="4" t="n">
@@ -2014,15 +2013,15 @@
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>Innsbruck (INN) / Bolzano (BZO) / Verona (VRN)</t>
+          <t>Verona (VRN) / Innsbruck (INN)</t>
         </is>
       </c>
       <c r="W14" s="4" t="n">
-        <v>119.9</v>
+        <v>192.2</v>
       </c>
       <c r="X14" s="4" t="inlineStr">
         <is>
-          <t>1h54 (INN) / 57min (BZO) / 2h21 (VRN)</t>
+          <t>2h21 (VRN) / 1h54 (INN)</t>
         </is>
       </c>
       <c r="Y14" s="4" t="n">
@@ -2678,15 +2677,15 @@
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>Turin (TRN) / Grenoble (GNB)</t>
+          <t>Lyon (LYS) / Turin (TRN) / Grenoble (GNB)</t>
         </is>
       </c>
       <c r="W19" s="4" t="n">
-        <v>136.4</v>
+        <v>211.9</v>
       </c>
       <c r="X19" s="4" t="inlineStr">
         <is>
-          <t>2h22 (TRN) / 3h00 (GNB)</t>
+          <t>3h26 (LYS) / 2h22 (TRN) / 3h00 (GNB)</t>
         </is>
       </c>
       <c r="Y19" s="4" t="n">
@@ -2995,50 +2994,50 @@
     <row r="22" ht="70" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Pamporovo</t>
+          <t>Kranjska Gora</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Rhodope Mountains</t>
+          <t>Julian Alps</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1450</v>
+        <v>810</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1926</v>
+        <v>1570</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>476</v>
+        <v>760</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>sourced_conflicting</t>
+          <t>estimated</t>
         </is>
       </c>
       <c r="M22" s="6" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
@@ -3047,7 +3046,7 @@
       </c>
       <c r="O22" s="6" t="inlineStr">
         <is>
-          <t>~mid Dec–early Apr</t>
+          <t>~mid Dec–late Mar</t>
         </is>
       </c>
       <c r="P22" s="6" t="inlineStr">
@@ -3057,7 +3056,7 @@
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>Good — Plovdiv/Sofia served by low-cost carriers; Bulgaria is the most Israeli-charter-friendly ski region overall</t>
+          <t>Indirect — via Ljubljana; no dedicated Israeli charter</t>
         </is>
       </c>
       <c r="R22" s="4" t="n">
@@ -3074,36 +3073,36 @@
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>Sofia (SOF) / Plovdiv (PDV)</t>
+          <t>Ljubljana (LJU) / Venice Marco Polo (VCE)</t>
         </is>
       </c>
       <c r="W22" s="4" t="n">
-        <v>225.2</v>
+        <v>63.7</v>
       </c>
       <c r="X22" s="4" t="inlineStr">
         <is>
-          <t>3h00 (SOF) / 1h29 (PDV)</t>
+          <t>50min (LJU) / 2h32 (VCE)</t>
         </is>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AA22" s="4" t="inlineStr">
         <is>
-          <t>NEEDS VERIFICATION (not individually sourced this pass). Small, low-key, very budget-friendly resort — cheapest option in this database; gentle, forested terrain suited to beginners/families rather than advanced/off-piste skiers; minimal nightlife compared to Bansko.</t>
+          <t>NEEDS VERIFICATION (not individually sourced this pass). Small, scenic, family-friendly resort hosting an annual World Cup slalom; low base elevation and modest vertical mean snow reliability is more weather-dependent; not a fit for off-piste/expert-focused trips.</t>
         </is>
       </c>
       <c r="AB22" s="4" t="inlineStr">
         <is>
-          <t>whatmegdidnext.com and an aggregated search summary (accessed Aug 2026)</t>
+          <t>General/prior knowledge — flagged for dedicated web verification pass</t>
         </is>
       </c>
       <c r="AC22" s="4" t="inlineStr">
         <is>
-          <t>Two sources disagree: one states 50% beginner/37% intermediate/12% black of 37km, another 59%/25%/16%. Same general shape (majority easy terrain, small black portion) but real numeric disagreement. This is a middle estimate, not a resolved figure.</t>
+          <t>Inferred from a qualitative description, not a published numeric breakdown.</t>
         </is>
       </c>
       <c r="AD22" s="4" t="inlineStr">
@@ -3113,10 +3112,10 @@
       </c>
       <c r="AE22" s="4" t="inlineStr"/>
       <c r="AF22" t="n">
-        <v>41.6553</v>
+        <v>46.4569</v>
       </c>
       <c r="AG22" t="n">
-        <v>24.6935</v>
+        <v>13.7782</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3127,260 +3126,264 @@
     <row r="23" ht="70" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Poiana Brasov</t>
+          <t>Val d'Isère / Tignes</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Southern Carpathians</t>
+          <t>Espace Killy</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1030</v>
+        <v>1550</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1775</v>
+        <v>3456</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>745</v>
+        <v>1906</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>24</v>
+        <v>300</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>estimated</t>
-        </is>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="N23" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O23" s="6" t="inlineStr">
-        <is>
-          <t>~mid Dec–late Mar</t>
-        </is>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>Small/unconfirmed</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>Indirect — via Bucharest; no dedicated Israeli charter, notably less popular with Israeli travelers than Bulgaria</t>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>625</v>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>Yes — Grande Motte glacier (Tignes side)</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>22 Nov–3 May</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>Indirect — via Chambéry/Geneva/Lyon; no dedicated Israeli charter</t>
         </is>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U23" s="4" t="n">
         <v>4</v>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>Bucharest (OTP) / Brasov (GHV)</t>
+          <t>Geneva (GVA) / Lyon (LYS) / Chambéry (CMF)</t>
         </is>
       </c>
       <c r="W23" s="4" t="n">
-        <v>156.6</v>
+        <v>177.6</v>
       </c>
       <c r="X23" s="4" t="inlineStr">
         <is>
-          <t>2h27 (OTP) / 31min (GHV)</t>
+          <t>2h52 (GVA) / 2h54 (LYS) / 2h10 (CMF)</t>
         </is>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>150</v>
+        <v>440</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="AA23" s="4" t="inlineStr">
         <is>
-          <t>NEEDS VERIFICATION (not individually sourced this pass). Very budget-friendly, small resort near the city of Brasov; limited piste count/lift capacity compared to Alpine resorts, best suited to a cheap short beginner/intermediate trip rather than a serious skiing-focused holiday.</t>
+          <t>Espace Killy is one of the largest and highest ski areas in the Alps, with year-round glacier skiing on the Grande Motte; Val d'Isère is more upmarket/scenic, Tignes (esp. Tignes Le Lac/Val Claret) is more purpose-built and popular with a younger, student/festival-going crowd; excellent snow reliability given the altitude.</t>
         </is>
       </c>
       <c r="AB23" s="4" t="inlineStr">
         <is>
-          <t>General/prior knowledge — flagged for dedicated web verification pass</t>
-        </is>
-      </c>
-      <c r="AC23" s="4" t="inlineStr">
-        <is>
-          <t>Inferred from a qualitative description, not a published numeric breakdown.</t>
-        </is>
-      </c>
+          <t>wikipedia.org, alpnav.com, ski-planet.com (accessed Aug 2026)</t>
+        </is>
+      </c>
+      <c r="AC23" s="4" t="n"/>
       <c r="AD23" s="4" t="inlineStr">
         <is>
-          <t>estimated</t>
-        </is>
-      </c>
-      <c r="AE23" s="4" t="inlineStr"/>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="AE23" s="4" t="inlineStr">
+        <is>
+          <t>Snowfall is an average of Val d'Isère (581cm) and Tignes (669cm) 10-year figures — the two sides differ. | TRANSFER CORRECTED (Aug 2026): Operators quote up to 2h45 from Geneva; sheet had 2h30.</t>
+        </is>
+      </c>
       <c r="AF23" t="n">
-        <v>45.597</v>
+        <v>45.4737</v>
       </c>
       <c r="AG23" t="n">
-        <v>25.5525</v>
+        <v>6.9496</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Open-Meteo geocoding API</t>
+          <t>Open-Meteo geocoding API (midpoint of Val d'Isere + Tignes, lift-linked Espace Killy resorts)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="70" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Kranjska Gora</t>
+          <t>Cortina d'Ampezzo</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Julian Alps</t>
+          <t>Dolomiti Superski</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>810</v>
+        <v>1224</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1570</v>
+        <v>3243</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>760</v>
+        <v>2019</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>estimated</t>
-        </is>
-      </c>
-      <c r="M24" s="6" t="n">
-        <v>250</v>
-      </c>
-      <c r="N24" s="6" t="inlineStr">
+          <t>sourced_conflicting</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O24" s="6" t="inlineStr">
-        <is>
-          <t>~mid Dec–late Mar</t>
-        </is>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>Small/unconfirmed</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>Indirect — via Ljubljana; no dedicated Israeli charter</t>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>29 Nov–3 May</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>Indirect — via Venice (VCE), the cheapest Alpine gateway priced in the 2026-08-29 probe at EUR430 round trip, or Innsbruck. Venice has no direct TLV service; Innsbruck has one Israir rotation a week on Fridays. The February 2026 Winter Olympics it co-hosted have now passed: the crowding and pricing distortion is over, the upgraded infrastructure remains.</t>
         </is>
       </c>
       <c r="R24" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>3</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>Ljubljana (LJU) / Venice Marco Polo (VCE)</t>
+          <t>Venice Marco Polo (VCE) / Innsbruck (INN)</t>
         </is>
       </c>
       <c r="W24" s="4" t="n">
-        <v>63.7</v>
+        <v>147.5</v>
       </c>
       <c r="X24" s="4" t="inlineStr">
         <is>
-          <t>50min (LJU) / 2h32 (VCE)</t>
+          <t>1h55 (VCE) / 2h39 (INN)</t>
         </is>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>220</v>
+        <v>380</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="AA24" s="4" t="inlineStr">
         <is>
-          <t>NEEDS VERIFICATION (not individually sourced this pass). Small, scenic, family-friendly resort hosting an annual World Cup slalom; low base elevation and modest vertical mean snow reliability is more weather-dependent; not a fit for off-piste/expert-focused trips.</t>
+          <t>Iconic Dolomites resort (hosted 1956 and co-hosted 2026 Winter Olympics) with dramatic limestone-peak scenery; on its own it's a moderate-sized, elegant, Italian-glamour resort, but the Dolomiti Superski pass unlocks the full 1,200+km Sella Ronda-region network; more about scenery/prestige/cuisine than hardcore off-piste.</t>
         </is>
       </c>
       <c r="AB24" s="4" t="inlineStr">
         <is>
-          <t>General/prior knowledge — flagged for dedicated web verification pass</t>
+          <t>j2ski.com, ultimate-ski.com, wikipedia.org (accessed Aug 2026)</t>
         </is>
       </c>
       <c r="AC24" s="4" t="inlineStr">
         <is>
-          <t>Inferred from a qualitative description, not a published numeric breakdown.</t>
+          <t>Published sources disagree substantially: one gives 33%/45%/16% beginner/intermediate/advanced, another ~33%/62%/5%, and a third (onthesnow.co.uk) uses a different intermediate/advanced/expert scheme with no beginner category at all. This is a middle estimate, not a resolved figure.</t>
         </is>
       </c>
       <c r="AD24" s="4" t="inlineStr">
         <is>
-          <t>estimated</t>
-        </is>
-      </c>
-      <c r="AE24" s="4" t="inlineStr"/>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AE24" s="4" t="inlineStr">
+        <is>
+          <t>Season dates sourced; snowfall estimated.</t>
+        </is>
+      </c>
       <c r="AF24" t="n">
-        <v>46.4569</v>
+        <v>46.5369</v>
       </c>
       <c r="AG24" t="n">
-        <v>13.7782</v>
+        <v>12.139</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -3391,7 +3394,7 @@
     <row r="25" ht="70" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Méribel</t>
+          <t>Les Deux Alpes</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -3401,29 +3404,29 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Les Trois Vallées</t>
+          <t>Isère / Alpe d'Huez region</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1450</v>
+        <v>1300</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2952</v>
+        <v>3600</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1502</v>
+        <v>2300</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>12</v>
@@ -3433,31 +3436,31 @@
           <t>sourced</t>
         </is>
       </c>
-      <c r="M25" s="5" t="n">
-        <v>380</v>
-      </c>
-      <c r="N25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>6 Dec–17 Apr</t>
-        </is>
-      </c>
-      <c r="P25" s="5" t="inlineStr">
+      <c r="M25" s="4" t="n">
+        <v>309</v>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>Yes — largest skiable glacier in Europe</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>29 Nov–3 May</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q25" s="5" t="inlineStr">
-        <is>
-          <t>Indirect — via Chambéry/Geneva on budget carriers; no dedicated Israeli charter</t>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>Indirect — via Grenoble/Lyon; no dedicated Israeli charter</t>
         </is>
       </c>
       <c r="R25" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S25" s="4" t="n">
         <v>4</v>
@@ -3466,53 +3469,49 @@
         <v>4</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>Geneva (GVA) / Chambéry (CMF)</t>
+          <t>Lyon (LYS) / Grenoble (GNB)</t>
         </is>
       </c>
       <c r="W25" s="4" t="n">
-        <v>77.90000000000001</v>
+        <v>167.2</v>
       </c>
       <c r="X25" s="4" t="inlineStr">
         <is>
-          <t>55min (GVA) / 1h17 (CMF)</t>
+          <t>2h19 (LYS) / 1h53 (GNB)</t>
         </is>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="AA25" s="4" t="inlineStr">
         <is>
-          <t>Sits at the geographic heart of the Trois Vallées, with easy day access to both Courchevel and Val Thorens on the full pass; large British expat presence gives it a lively, English-friendly nightlife scene (La Folie Douce, Le Rond Point); some of the 3 Vallées' best off-piste freeride is here despite its reputation as an intermediate cruiser's resort.</t>
+          <t>Has the largest skiable glacier in Europe and one of the longest lift-served on-piste verticals in the world; foot access to the famous off-piste resort La Grave from the top of the glacier; good party-town nightlife reputation; closer to Grenoble than most major French resorts.</t>
         </is>
       </c>
       <c r="AB25" s="4" t="inlineStr">
         <is>
-          <t>powderhounds.com, j2ski.com, wikipedia.org, alpinefleet.com, weski.com (accessed Aug 2026)</t>
+          <t>wikipedia.org (accessed Aug 2026)</t>
         </is>
       </c>
       <c r="AC25" s="4" t="n"/>
       <c r="AD25" s="4" t="inlineStr">
         <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AE25" s="4" t="inlineStr">
-        <is>
-          <t>Season dates sourced; snowfall estimated by 3 Vallées regional comparison. | TRANSFER CORRECTED (Aug 2026): Operators quote 2h30 from Geneva; sheet had 2h15.</t>
-        </is>
-      </c>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="AE25" s="4" t="inlineStr"/>
       <c r="AF25" t="n">
-        <v>45.415</v>
+        <v>45.0116</v>
       </c>
       <c r="AG25" t="n">
-        <v>6.565</v>
+        <v>6.1255</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -3523,7 +3522,7 @@
     <row r="26" ht="70" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Val d'Isère / Tignes</t>
+          <t>Grand Massif (Flaine)</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -3533,2399 +3532,1069 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Espace Killy</t>
+          <t>Haute-Savoie</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1550</v>
+        <v>700</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3456</v>
+        <v>2561</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1906</v>
+        <v>1861</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>300</v>
+        <v>265</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
           <t>sourced</t>
         </is>
       </c>
-      <c r="M26" s="4" t="n">
-        <v>625</v>
-      </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>Yes — Grande Motte glacier (Tignes side)</t>
-        </is>
-      </c>
-      <c r="O26" s="4" t="inlineStr">
-        <is>
-          <t>22 Nov–3 May</t>
-        </is>
-      </c>
-      <c r="P26" s="4" t="inlineStr">
+      <c r="M26" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>6 Dec–19 Apr</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>Indirect — via Chambéry/Geneva/Lyon; no dedicated Israeli charter</t>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>Indirect — via Geneva on budget carriers; no dedicated Israeli charter</t>
         </is>
       </c>
       <c r="R26" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S26" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="S26" s="4" t="n">
-        <v>5</v>
-      </c>
       <c r="T26" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U26" s="4" t="n">
         <v>4</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>Geneva (GVA) / Lyon (LYS) / Chambéry (CMF)</t>
+          <t>Geneva (GVA)</t>
         </is>
       </c>
       <c r="W26" s="4" t="n">
-        <v>177.6</v>
+        <v>89</v>
       </c>
       <c r="X26" s="4" t="inlineStr">
         <is>
-          <t>2h52 (GVA) / 2h54 (LYS) / 2h10 (CMF)</t>
+          <t>1h17 (GVA)</t>
         </is>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>440</v>
+        <v>340</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="AA26" s="4" t="inlineStr">
         <is>
-          <t>Espace Killy is one of the largest and highest ski areas in the Alps, with year-round glacier skiing on the Grande Motte; Val d'Isère is more upmarket/scenic, Tignes (esp. Tignes Le Lac/Val Claret) is more purpose-built and popular with a younger, student/festival-going crowd; excellent snow reliability given the altitude.</t>
+          <t>Linked network of Flaine, Samoëns, Morillon, Les Carroz and Sixt; Flaine itself has a strong snow record ('the big snowy bowl') but 1960s brutalist architecture that's an acquired taste; one of the shortest Geneva transfers in this database, useful for a quick trip.</t>
         </is>
       </c>
       <c r="AB26" s="4" t="inlineStr">
         <is>
-          <t>wikipedia.org, alpnav.com, ski-planet.com (accessed Aug 2026)</t>
+          <t>wikipedia.org (accessed Aug 2026)</t>
         </is>
       </c>
       <c r="AC26" s="4" t="n"/>
       <c r="AD26" s="4" t="inlineStr">
         <is>
-          <t>sourced</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AE26" s="4" t="inlineStr">
         <is>
-          <t>Snowfall is an average of Val d'Isère (581cm) and Tignes (669cm) 10-year figures — the two sides differ. | TRANSFER CORRECTED (Aug 2026): Operators quote up to 2h45 from Geneva; sheet had 2h30.</t>
+          <t>Season dates sourced; snowfall estimated.</t>
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>45.4737</v>
+        <v>46.0066</v>
       </c>
       <c r="AG26" t="n">
-        <v>6.9496</v>
+        <v>6.6896</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Open-Meteo geocoding API (midpoint of Val d'Isere + Tignes, lift-linked Espace Killy resorts)</t>
+          <t>Open-Meteo geocoding API</t>
         </is>
       </c>
     </row>
     <row r="27" ht="70" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Obergurgl-Hochgurgl</t>
+          <t>Bardonecchia</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Milky Way (Via Lattea) / Piedmont</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>1312</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>2750</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1438</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>280</v>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>~early Dec–mid Apr</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Indirect — via Turin, the closest major resort to Turin airport in this database; no dedicated Israeli charter</t>
+        </is>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="V27" s="4" t="inlineStr">
+        <is>
+          <t>Turin (TRN)</t>
+        </is>
+      </c>
+      <c r="W27" s="4" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="X27" s="4" t="inlineStr">
+        <is>
+          <t>1h17 (TRN)</t>
+        </is>
+      </c>
+      <c r="Y27" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="Z27" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA27" s="4" t="inlineStr">
+        <is>
+          <t>NEEDS VERIFICATION (not individually sourced this pass). Part of the large Milky Way (Via Lattea) linked area shared with Sestriere and Sauze d'Oulx; closest major resort to Turin airport in this database, and generally cheaper than French/Swiss/Austrian equivalents.</t>
+        </is>
+      </c>
+      <c r="AB27" s="4" t="inlineStr">
+        <is>
+          <t>General/prior knowledge — flagged for dedicated web verification pass</t>
+        </is>
+      </c>
+      <c r="AC27" s="4" t="inlineStr">
+        <is>
+          <t>Inferred from a qualitative description, not a published numeric breakdown.</t>
+        </is>
+      </c>
+      <c r="AD27" s="4" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="AE27" s="4" t="inlineStr"/>
+      <c r="AF27" t="n">
+        <v>45.0746</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>6.6989</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="70" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Passo Tonale</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pontedilegno-Tonale</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1883</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3088</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1205</v>
+      </c>
+      <c r="G28" t="n">
+        <v>27</v>
+      </c>
+      <c r="H28" t="n">
+        <v>100</v>
+      </c>
+      <c r="I28" t="n">
+        <v>28</v>
+      </c>
+      <c r="J28" t="n">
+        <v>55</v>
+      </c>
+      <c r="K28" t="n">
+        <v>17</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>450</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Limited — Presena Glacier run</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>~14 Oct–mid Jun (glacier-extended; core season shorter)</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Indirect — via Bolzano/Milan Bergamo; no dedicated Israeli charter</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>5</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Verona (VRN) / Milan Bergamo (BGY)</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2h29 (VRN) / 2h12 (BGY)</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>190</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>NEEDS VERIFICATION (not individually sourced this pass). Genuinely family-oriented -- pedestrian-friendly centre, ski-in-ski-out accommodation, easy slopes right from the resort. Presena Glacier gives snow-sure terrain at altitude for a resort with a relatively modest base.</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>skiclub.co.uk, j2ski.com, pontedilegnotonale.com (accessed Aug 2026)</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>28% blue/22 red/17% black per pontedilegnotonale.com's own published split (rounded to sum 100).</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>Season dates, piste km, lifts, terrain % and ski pass range sourced; snowfall, accommodation price and 1-5 ratings estimated. Snowfall ESTIMATED: only a single 'snowiest week' data point (43cm) was found, scaled to a plausible seasonal total by comparison to similar-altitude Alpine resorts already in this database -- not a direct annual citation.</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
+        <v>46.26073</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>10.58726</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="70" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mayrhofen</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Ötztal Valley</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>1793</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>3082</v>
-      </c>
-      <c r="F27" s="4" t="n">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Zillertal Valley</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>630</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1870</v>
+      </c>
+      <c r="G29" t="n">
+        <v>45</v>
+      </c>
+      <c r="H29" t="n">
+        <v>142</v>
+      </c>
+      <c r="I29" t="n">
+        <v>30</v>
+      </c>
+      <c r="J29" t="n">
+        <v>49</v>
+      </c>
+      <c r="K29" t="n">
+        <v>21</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>219</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>No — nearest glacier (Hintertux) is a separate resort up-valley</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Early Dec–mid Apr</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Good — Innsbruck has direct scheduled flights (Israir) this season, ~1h away</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Innsbruck (INN) / Munich (MUC)</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>1h05 (INN) / 2h14 (MUC)</t>
+        </is>
+      </c>
+      <c r="Y29" t="n">
+        <v>360</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>135</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>NEEDS VERIFICATION (not individually sourced this pass). Renowned specifically for long-running, high-volume apres-ski (arguably the standout nightlife resort in this database) -- a genuinely distinct positioning. Also has real steep terrain (Harakiri, Austria's steepest marked piste) despite a low, snow-marginal base elevation (630m).</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>j2ski.com, welove2ski.com, inthesnow.com (accessed Aug 2026)</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>30% blue/49% red/21% black per an aggregated piste-map summary (no separate green count found; likely folded into 'blue').</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>Terrain %, lifts, piste km, season and snowfall sourced; ski pass price, accommodation price and 1-5 ratings estimated.</t>
+        </is>
+      </c>
+      <c r="AF29" t="n">
+        <v>47.16667</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>11.86667</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="70" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Zell am See</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Zell am See-Kaprun</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>757</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3029</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2272</v>
+      </c>
+      <c r="G30" t="n">
+        <v>28</v>
+      </c>
+      <c r="H30" t="n">
+        <v>138</v>
+      </c>
+      <c r="I30" t="n">
+        <v>35</v>
+      </c>
+      <c r="J30" t="n">
+        <v>45</v>
+      </c>
+      <c r="K30" t="n">
+        <v>20</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>455</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Yes — Kitzsteinhorn glacier is part of the linked ski area</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Mid Oct–late May (glacier-extended)</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Good — Salzburg has had seasonal direct flights (Sun D'Or) in recent years</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>3</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Salzburg (SZG) / Munich (MUC)</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>1h16 (SZG) / 2h37 (MUC)</t>
+        </is>
+      </c>
+      <c r="Y30" t="n">
+        <v>370</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>140</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>NEEDS VERIFICATION (not individually sourced this pass). Two linked mountains on one pass -- Schmittenhoehe skews intermediate, Kaprun's Maiskogel has a dedicated nursery slope and wide, gentle terrain for families; glacier skiing at Kitzsteinhorn adds snow security most low/mid-elevation Austrian resorts lack. Free connecting ski bus between the two base towns.</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>j2ski.com, powderhounds.com, snowplaza.co.uk (accessed Aug 2026)</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>35% beginner/45% intermediate/20% advanced per an aggregated piste-map summary.</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>Terrain %, elevation, lifts, piste km, season and snowfall sourced; ski pass price, accommodation price and 1-5 ratings estimated.</t>
+        </is>
+      </c>
+      <c r="AF30" t="n">
+        <v>47.32306</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>12.79839</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="70" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Les Arcs</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Paradiski</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3226</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G31" t="n">
+        <v>82</v>
+      </c>
+      <c r="H31" t="n">
+        <v>200</v>
+      </c>
+      <c r="I31" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" t="n">
+        <v>42</v>
+      </c>
+      <c r="K31" t="n">
+        <v>48</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>500</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Mid Dec–late Apr</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Indirect — via Chambéry/Geneva; no dedicated Israeli charter</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Geneva (GVA) / Chambéry (CMF)</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>2h33 (GVA) / 1h50 (CMF)</t>
+        </is>
+      </c>
+      <c r="Y31" t="n">
+        <v>368</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>NEEDS VERIFICATION (not individually sourced this pass). Cable-car linked to La Plagne (Paradiski, 425km combined) -- the steepest terrain skew of any resort in this database (48% advanced/expert). High-altitude and snow-secure (summit 3,226m); this is the same Paradiski link that made La Plagne itself come up in the same skideal.co.il research pass, though La Plagne isn't sold as its own package there.</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>wikipedia.org, j2ski.com, skibeat.co.uk, lesarcs-peiseyvallandry.com (accessed Aug 2026)</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>10% beginner/42% intermediate/34% advanced/14% expert per aggregated piste stats; advanced+expert folded together for this database's 3-way schema.</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>Elevation, lifts, piste km, terrain %, season and ski pass price sourced; snowfall, accommodation price and 1-5 ratings estimated. Airport distance has real source disagreement (120-140km). Snowfall ESTIMATED by comparison to Val Thorens (643cm, same general altitude band, already in this database) adjusted down for Les Arcs' lower base elevation -- no direct citation found.</t>
+        </is>
+      </c>
+      <c r="AF31" t="n">
+        <v>45.57755</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>6.78165</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="70" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Les Menuires</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Les Trois Vallées</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2850</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G32" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" t="n">
+        <v>160</v>
+      </c>
+      <c r="I32" t="n">
+        <v>61</v>
+      </c>
+      <c r="J32" t="n">
+        <v>32</v>
+      </c>
+      <c r="K32" t="n">
+        <v>8</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>450</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Early Dec–mid Apr</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Indirect — via Chambéry/Geneva; no dedicated Israeli charter</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>3</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Geneva (GVA) / Chambéry (CMF)</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>145.6</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>2h19 (GVA) / 1h36 (CMF)</t>
+        </is>
+      </c>
+      <c r="Y32" t="n">
+        <v>315</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>NEEDS VERIFICATION (not individually sourced this pass). The value/budget base of Les 3 Vallées -- the same lift network already covered here via Courchevel, Méribel and Val Thorens, giving this database its first cheaper entry point into that circuit. 85% of terrain sits above 1,800m, genuinely snow-secure for its price tier.</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>powderhounds.com, j2ski.com, alps2alps.com (accessed Aug 2026)</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>12 green + 34 blue + 24 red + 6 black of 76 trails (count-based).</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>Elevation, lifts, piste km, terrain %, season and ski pass price sourced; snowfall, accommodation price and 1-5 ratings estimated. Snowfall ESTIMATED by comparison to Val Thorens (643cm, same Trois Vallées circuit, already in this database) adjusted down for Les Menuires' lower base elevation -- no direct citation found.</t>
+        </is>
+      </c>
+      <c r="AF32" t="n">
+        <v>45.32293</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>6.53757</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Open-Meteo geocoding API</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="70" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Gudauri</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Greater Caucasus (Kazbegi)</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1990</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3279</v>
+      </c>
+      <c r="F33" t="n">
         <v>1289</v>
       </c>
-      <c r="G27" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>112</v>
-      </c>
-      <c r="I27" s="4" t="n">
+      <c r="G33" t="n">
+        <v>20</v>
+      </c>
+      <c r="H33" t="n">
+        <v>76</v>
+      </c>
+      <c r="I33" t="n">
         <v>30</v>
       </c>
-      <c r="J27" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="J33" t="n">
+        <v>50</v>
+      </c>
+      <c r="K33" t="n">
+        <v>20</v>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>estimated</t>
         </is>
       </c>
-      <c r="M27" s="5" t="n">
+      <c r="M33" t="n">
         <v>350</v>
       </c>
-      <c r="N27" s="5" t="inlineStr">
-        <is>
-          <t>No — but very high altitude (3,082m top)</t>
-        </is>
-      </c>
-      <c r="O27" s="5" t="inlineStr">
-        <is>
-          <t>20 Nov–~20 Apr</t>
-        </is>
-      </c>
-      <c r="P27" s="5" t="inlineStr">
-        <is>
-          <t>Small/unconfirmed — quiet, family-oriented resort</t>
-        </is>
-      </c>
-      <c r="Q27" s="5" t="inlineStr">
-        <is>
-          <t>Good — Innsbruck has direct scheduled flights (Israir) this season</t>
-        </is>
-      </c>
-      <c r="R27" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S27" s="4" t="n">
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>~late Dec–mid Apr (high-altitude, opens ~Dec 27)</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Excellent — Tbilisi (TBS) has direct scheduled TLV service year-round (probed live 2026-08-28: EUR400 Oct / EUR766 Jan round trips priced on Google Flights); one of the largest Israeli ski markets outside Europe</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
         <v>5</v>
       </c>
-      <c r="T27" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U27" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="V27" s="4" t="inlineStr">
-        <is>
-          <t>Innsbruck (INN)</t>
-        </is>
-      </c>
-      <c r="W27" s="4" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="X27" s="4" t="inlineStr">
-        <is>
-          <t>1h34 (INN)</t>
-        </is>
-      </c>
-      <c r="Y27" s="4" t="n">
-        <v>430</v>
-      </c>
-      <c r="Z27" s="4" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA27" s="4" t="inlineStr">
-        <is>
-          <t>One of the highest, most snow-sure villages in the Alps (skiing guaranteed mid-Nov to early May); quiet, upmarket, family/couple-oriented rather than nightlife-focused — the opposite profile from Ischgl/St Anton despite being in the same general region; linked by bus/pass-sharing to the much larger Sölden area for guests who want more terrain variety.</t>
-        </is>
-      </c>
-      <c r="AB27" s="4" t="inlineStr">
-        <is>
-          <t>ultimate-ski.com, welove2ski.com, weski.com, gurgl.com, ski-austria.com (accessed Aug 2026)</t>
-        </is>
-      </c>
-      <c r="AC27" s="4" t="inlineStr">
-        <is>
-          <t>Inferred from a qualitative description, not a published numeric breakdown.</t>
-        </is>
-      </c>
-      <c r="AD27" s="4" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AE27" s="4" t="inlineStr">
-        <is>
-          <t>Opening date and flight access sourced; snowfall/closing estimated.</t>
-        </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>46.8667</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>11.0167</v>
-      </c>
-      <c r="AH27" t="inlineStr">
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Tbilisi (TBS)</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2h35 (TBS)</t>
+        </is>
+      </c>
+      <c r="Y33" t="n">
+        <v>116</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Highest-value freeride destination in the database: entirely above the tree line, 1,990-3,279m, famous for accessible off-piste and heliskiing; modern Doppelmayr lifts; nightlife modest, resort is purpose-built. 6-day pass 340 GEL (~EUR116). Accommodation figure estimated.</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>skiresort.com, gudauri.com, snow-forecast.com, j2ski.com (accessed Aug 2026)</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>Terrain split estimated from qualitative guides; pass converted from GEL.</t>
+        </is>
+      </c>
+      <c r="AF33" t="n">
+        <v>42.4796</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>44.4805</v>
+      </c>
+      <c r="AH33" t="inlineStr">
         <is>
           <t>Open-Meteo geocoding API</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="70" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Cortina d'Ampezzo</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Dolomiti Superski</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>1224</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>3243</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>2019</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>sourced_conflicting</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>29 Nov–3 May</t>
-        </is>
-      </c>
-      <c r="P28" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q28" s="5" t="inlineStr">
-        <is>
-          <t>Indirect — via Venice/Innsbruck; co-hosted the 2026 Winter Olympics, which may affect pricing/crowds around that period</t>
-        </is>
-      </c>
-      <c r="R28" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S28" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T28" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U28" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="V28" s="4" t="inlineStr">
-        <is>
-          <t>Venice Marco Polo (VCE) / Innsbruck (INN)</t>
-        </is>
-      </c>
-      <c r="W28" s="4" t="n">
-        <v>147.5</v>
-      </c>
-      <c r="X28" s="4" t="inlineStr">
-        <is>
-          <t>1h55 (VCE) / 2h39 (INN)</t>
-        </is>
-      </c>
-      <c r="Y28" s="4" t="n">
-        <v>380</v>
-      </c>
-      <c r="Z28" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="AA28" s="4" t="inlineStr">
-        <is>
-          <t>Iconic Dolomites resort (hosted 1956 and co-hosted 2026 Winter Olympics) with dramatic limestone-peak scenery; on its own it's a moderate-sized, elegant, Italian-glamour resort, but the Dolomiti Superski pass unlocks the full 1,200+km Sella Ronda-region network; more about scenery/prestige/cuisine than hardcore off-piste.</t>
-        </is>
-      </c>
-      <c r="AB28" s="4" t="inlineStr">
-        <is>
-          <t>j2ski.com, ultimate-ski.com, wikipedia.org (accessed Aug 2026)</t>
-        </is>
-      </c>
-      <c r="AC28" s="4" t="inlineStr">
-        <is>
-          <t>Published sources disagree substantially: one gives 33%/45%/16% beginner/intermediate/advanced, another ~33%/62%/5%, and a third (onthesnow.co.uk) uses a different intermediate/advanced/expert scheme with no beginner category at all. This is a middle estimate, not a resolved figure.</t>
-        </is>
-      </c>
-      <c r="AD28" s="4" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AE28" s="4" t="inlineStr">
-        <is>
-          <t>Season dates sourced; snowfall estimated.</t>
-        </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>46.5369</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>12.139</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Open-Meteo geocoding API</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="70" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Les Deux Alpes</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Isère / Alpe d'Huez region</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>1300</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>2300</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>sourced</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v>309</v>
-      </c>
-      <c r="N29" s="4" t="inlineStr">
-        <is>
-          <t>Yes — largest skiable glacier in Europe</t>
-        </is>
-      </c>
-      <c r="O29" s="4" t="inlineStr">
-        <is>
-          <t>29 Nov–3 May</t>
-        </is>
-      </c>
-      <c r="P29" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q29" s="4" t="inlineStr">
-        <is>
-          <t>Indirect — via Grenoble/Lyon; no dedicated Israeli charter</t>
-        </is>
-      </c>
-      <c r="R29" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S29" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T29" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="U29" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="V29" s="4" t="inlineStr">
-        <is>
-          <t>Lyon (LYS) / Grenoble (GNB)</t>
-        </is>
-      </c>
-      <c r="W29" s="4" t="n">
-        <v>167.2</v>
-      </c>
-      <c r="X29" s="4" t="inlineStr">
-        <is>
-          <t>2h19 (LYS) / 1h53 (GNB)</t>
-        </is>
-      </c>
-      <c r="Y29" s="4" t="n">
-        <v>350</v>
-      </c>
-      <c r="Z29" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA29" s="4" t="inlineStr">
-        <is>
-          <t>Has the largest skiable glacier in Europe and one of the longest lift-served on-piste verticals in the world; foot access to the famous off-piste resort La Grave from the top of the glacier; good party-town nightlife reputation; closer to Grenoble than most major French resorts.</t>
-        </is>
-      </c>
-      <c r="AB29" s="4" t="inlineStr">
-        <is>
-          <t>wikipedia.org (accessed Aug 2026)</t>
-        </is>
-      </c>
-      <c r="AC29" s="4" t="n"/>
-      <c r="AD29" s="4" t="inlineStr">
-        <is>
-          <t>sourced</t>
-        </is>
-      </c>
-      <c r="AE29" s="4" t="inlineStr"/>
-      <c r="AF29" t="n">
-        <v>45.0116</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>6.1255</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Open-Meteo geocoding API</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="70" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Formigal</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Aragonese Pyrenees</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>2250</v>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>740</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>176</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="K30" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>estimated</t>
-        </is>
-      </c>
-      <c r="M30" s="6" t="n">
-        <v>250</v>
-      </c>
-      <c r="N30" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O30" s="6" t="inlineStr">
-        <is>
-          <t>~early Dec–mid Apr</t>
-        </is>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>Indirect and limited — via Zaragoza or Lourdes (France); the least convenient routing from Israel in this database</t>
-        </is>
-      </c>
-      <c r="R30" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S30" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T30" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="U30" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="V30" s="4" t="inlineStr">
-        <is>
-          <t>Barcelona (BCN) / Zaragoza (ZAZ)</t>
-        </is>
-      </c>
-      <c r="W30" s="4" t="n">
-        <v>352.7</v>
-      </c>
-      <c r="X30" s="4" t="inlineStr">
-        <is>
-          <t>3h47 (BCN) / 2h01 (ZAZ)</t>
-        </is>
-      </c>
-      <c r="Y30" s="4" t="n">
-        <v>260</v>
-      </c>
-      <c r="Z30" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA30" s="4" t="inlineStr">
-        <is>
-          <t>Largest ski area in the Pyrenees, jointly ticketed with neighboring Panticosa; good value vs the Alps and a solid nightlife scene by Pyrenean standards; flight options from Israel are more limited/indirect than to the main Alpine hubs, worth checking routing before shortlisting.</t>
-        </is>
-      </c>
-      <c r="AB30" s="4" t="inlineStr">
-        <is>
-          <t>wikipedia.org (accessed Aug 2026)</t>
-        </is>
-      </c>
-      <c r="AC30" s="4" t="inlineStr">
-        <is>
-          <t>Inferred from a qualitative description, not a published numeric breakdown.</t>
-        </is>
-      </c>
-      <c r="AD30" s="4" t="inlineStr">
-        <is>
-          <t>estimated</t>
-        </is>
-      </c>
-      <c r="AE30" s="4" t="inlineStr"/>
-      <c r="AF30" t="n">
-        <v>42.7771</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>-0.3593</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Open-Meteo geocoding API</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="70" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Grand Massif (Flaine)</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Haute-Savoie</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>700</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>2561</v>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>1861</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>265</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>sourced</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="N31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O31" s="5" t="inlineStr">
-        <is>
-          <t>6 Dec–19 Apr</t>
-        </is>
-      </c>
-      <c r="P31" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q31" s="5" t="inlineStr">
-        <is>
-          <t>Indirect — via Geneva on budget carriers; no dedicated Israeli charter</t>
-        </is>
-      </c>
-      <c r="R31" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S31" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T31" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U31" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="V31" s="4" t="inlineStr">
-        <is>
-          <t>Geneva (GVA)</t>
-        </is>
-      </c>
-      <c r="W31" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="X31" s="4" t="inlineStr">
-        <is>
-          <t>1h17 (GVA)</t>
-        </is>
-      </c>
-      <c r="Y31" s="4" t="n">
-        <v>340</v>
-      </c>
-      <c r="Z31" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA31" s="4" t="inlineStr">
-        <is>
-          <t>Linked network of Flaine, Samoëns, Morillon, Les Carroz and Sixt; Flaine itself has a strong snow record ('the big snowy bowl') but 1960s brutalist architecture that's an acquired taste; one of the shortest Geneva transfers in this database, useful for a quick trip.</t>
-        </is>
-      </c>
-      <c r="AB31" s="4" t="inlineStr">
-        <is>
-          <t>wikipedia.org (accessed Aug 2026)</t>
-        </is>
-      </c>
-      <c r="AC31" s="4" t="n"/>
-      <c r="AD31" s="4" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AE31" s="4" t="inlineStr">
-        <is>
-          <t>Season dates sourced; snowfall estimated.</t>
-        </is>
-      </c>
-      <c r="AF31" t="n">
-        <v>46.0066</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>6.6896</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Open-Meteo geocoding API</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="70" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Krvavec</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Kamnik-Savinja Alps</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>1450</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>1971</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>521</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>estimated</t>
-        </is>
-      </c>
-      <c r="M32" s="6" t="n">
-        <v>280</v>
-      </c>
-      <c r="N32" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O32" s="6" t="inlineStr">
-        <is>
-          <t>~mid Dec–late Mar</t>
-        </is>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>Small/unconfirmed</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>Indirect — via Ljubljana (10km transfer, shortest in this database); no dedicated Israeli charter</t>
-        </is>
-      </c>
-      <c r="R32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T32" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t>Ljubljana (LJU) / Venice Marco Polo (VCE)</t>
-        </is>
-      </c>
-      <c r="W32" s="4" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X32" s="4" t="inlineStr">
-        <is>
-          <t>42min (LJU) / 3h16 (VCE)</t>
-        </is>
-      </c>
-      <c r="Y32" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="Z32" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AA32" s="4" t="inlineStr">
-        <is>
-          <t>NEEDS VERIFICATION (not individually sourced this pass — elevation/lift facts came from a general search, not a dedicated resort-site check). Remarkable for being just ~10km from Ljubljana airport — the shortest transfer of any resort in this database — making it viable even for a very short/cheap trip; small ski area, not a fit for a serious multi-day ski-focused holiday.</t>
-        </is>
-      </c>
-      <c r="AB32" s="4" t="inlineStr">
-        <is>
-          <t>General/prior knowledge — flagged for dedicated web verification pass</t>
-        </is>
-      </c>
-      <c r="AC32" s="4" t="inlineStr">
-        <is>
-          <t>Inferred from a qualitative description, not a published numeric breakdown.</t>
-        </is>
-      </c>
-      <c r="AD32" s="4" t="inlineStr">
-        <is>
-          <t>estimated</t>
-        </is>
-      </c>
-      <c r="AE32" s="4" t="inlineStr"/>
-      <c r="AF32" t="n">
-        <v>46.2972</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>14.5325</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>corrected by hand 2026-08-29 (geocoder had placed it 69km west)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="70" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Astún-Candanchú</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Aragonese Pyrenees</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>1700</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>2300</v>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>600</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>estimated</t>
-        </is>
-      </c>
-      <c r="M33" s="6" t="n">
-        <v>250</v>
-      </c>
-      <c r="N33" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O33" s="6" t="inlineStr">
-        <is>
-          <t>~early Dec–mid Apr</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>Small/unconfirmed</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>Indirect and limited — via Zaragoza or Pau (France); alongside Formigal, the least convenient routing from Israel in this database</t>
-        </is>
-      </c>
-      <c r="R33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S33" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T33" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U33" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="V33" s="4" t="inlineStr">
-        <is>
-          <t>Barcelona (BCN) / Zaragoza (ZAZ)</t>
-        </is>
-      </c>
-      <c r="W33" s="4" t="n">
-        <v>362.5</v>
-      </c>
-      <c r="X33" s="4" t="inlineStr">
-        <is>
-          <t>3h49 (BCN) / 2h03 (ZAZ)</t>
-        </is>
-      </c>
-      <c r="Y33" s="4" t="n">
-        <v>220</v>
-      </c>
-      <c r="Z33" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AA33" s="4" t="inlineStr">
-        <is>
-          <t>NEEDS VERIFICATION (not individually sourced this pass — combined estimate for the jointly-passed Astún + Candanchú resorts). Budget Pyrenean option, smaller and quieter than Formigal; limited flight routing from Israel is the main practical obstacle.</t>
-        </is>
-      </c>
-      <c r="AB33" s="4" t="inlineStr">
-        <is>
-          <t>General/prior knowledge — flagged for dedicated web verification pass</t>
-        </is>
-      </c>
-      <c r="AC33" s="4" t="inlineStr">
-        <is>
-          <t>Inferred from a qualitative description, not a published numeric breakdown.</t>
-        </is>
-      </c>
-      <c r="AD33" s="4" t="inlineStr">
-        <is>
-          <t>estimated</t>
-        </is>
-      </c>
-      <c r="AE33" s="4" t="inlineStr"/>
-      <c r="AF33" t="n">
-        <v>42.7878</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>-0.5288</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Open-Meteo geocoding API</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="70" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Bardonecchia</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Milky Way (Via Lattea) / Piedmont</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>1312</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>2750</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>1438</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="K34" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>estimated</t>
-        </is>
-      </c>
-      <c r="M34" s="6" t="n">
-        <v>280</v>
-      </c>
-      <c r="N34" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O34" s="6" t="inlineStr">
-        <is>
-          <t>~early Dec–mid Apr</t>
-        </is>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>Indirect — via Turin, the closest major resort to Turin airport in this database; no dedicated Israeli charter</t>
-        </is>
-      </c>
-      <c r="R34" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S34" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T34" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U34" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="V34" s="4" t="inlineStr">
-        <is>
-          <t>Turin (TRN)</t>
-        </is>
-      </c>
-      <c r="W34" s="4" t="n">
-        <v>102.8</v>
-      </c>
-      <c r="X34" s="4" t="inlineStr">
-        <is>
-          <t>1h17 (TRN)</t>
-        </is>
-      </c>
-      <c r="Y34" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="Z34" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA34" s="4" t="inlineStr">
-        <is>
-          <t>NEEDS VERIFICATION (not individually sourced this pass). Part of the large Milky Way (Via Lattea) linked area shared with Sestriere and Sauze d'Oulx; closest major resort to Turin airport in this database, and generally cheaper than French/Swiss/Austrian equivalents.</t>
-        </is>
-      </c>
-      <c r="AB34" s="4" t="inlineStr">
-        <is>
-          <t>General/prior knowledge — flagged for dedicated web verification pass</t>
-        </is>
-      </c>
-      <c r="AC34" s="4" t="inlineStr">
-        <is>
-          <t>Inferred from a qualitative description, not a published numeric breakdown.</t>
-        </is>
-      </c>
-      <c r="AD34" s="4" t="inlineStr">
-        <is>
-          <t>estimated</t>
-        </is>
-      </c>
-      <c r="AE34" s="4" t="inlineStr"/>
-      <c r="AF34" t="n">
-        <v>45.0746</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>6.6989</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Open-Meteo geocoding API</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Passo Tonale</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Pontedilegno-Tonale</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>1883</v>
-      </c>
-      <c r="E35" t="n">
-        <v>3088</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1205</v>
-      </c>
-      <c r="G35" t="n">
-        <v>27</v>
-      </c>
-      <c r="H35" t="n">
-        <v>100</v>
-      </c>
-      <c r="I35" t="n">
-        <v>28</v>
-      </c>
-      <c r="J35" t="n">
-        <v>55</v>
-      </c>
-      <c r="K35" t="n">
-        <v>17</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>sourced</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
-        <v>450</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Limited — Presena Glacier run</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>~14 Oct–mid Jun (glacier-extended; core season shorter)</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Indirect — via Bolzano/Milan Bergamo; no dedicated Israeli charter</t>
-        </is>
-      </c>
-      <c r="R35" t="n">
-        <v>2</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>5</v>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Milan Bergamo (BGY) / Verona (VRN) / Bolzano (BZO)</t>
-        </is>
-      </c>
-      <c r="W35" t="n">
-        <v>127.3</v>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>2h12 (BGY) / 2h29 (VRN) / 1h51 (BZO)</t>
-        </is>
-      </c>
-      <c r="Y35" t="n">
-        <v>190</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>NEEDS VERIFICATION (not individually sourced this pass). Genuinely family-oriented -- pedestrian-friendly centre, ski-in-ski-out accommodation, easy slopes right from the resort. Presena Glacier gives snow-sure terrain at altitude for a resort with a relatively modest base.</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>skiclub.co.uk, j2ski.com, pontedilegnotonale.com (accessed Aug 2026)</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>28% blue/22 red/17% black per pontedilegnotonale.com's own published split (rounded to sum 100).</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>Season dates, piste km, lifts, terrain % and ski pass range sourced; snowfall, accommodation price and 1-5 ratings estimated. Snowfall ESTIMATED: only a single 'snowiest week' data point (43cm) was found, scaled to a plausible seasonal total by comparison to similar-altitude Alpine resorts already in this database -- not a direct annual citation.</t>
-        </is>
-      </c>
-      <c r="AF35" t="n">
-        <v>46.26073</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>10.58726</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Open-Meteo geocoding API</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Mayrhofen</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Zillertal Valley</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>630</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1870</v>
-      </c>
-      <c r="G36" t="n">
-        <v>45</v>
-      </c>
-      <c r="H36" t="n">
-        <v>142</v>
-      </c>
-      <c r="I36" t="n">
-        <v>30</v>
-      </c>
-      <c r="J36" t="n">
-        <v>49</v>
-      </c>
-      <c r="K36" t="n">
-        <v>21</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>sourced</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
-        <v>219</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>No — nearest glacier (Hintertux) is a separate resort up-valley</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Early Dec–mid Apr</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Good — Innsbruck has direct scheduled flights (Israir) this season, ~1h away</t>
-        </is>
-      </c>
-      <c r="R36" t="n">
-        <v>3</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>5</v>
-      </c>
-      <c r="U36" t="n">
-        <v>3</v>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Innsbruck (INN) / Munich (MUC)</t>
-        </is>
-      </c>
-      <c r="W36" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>1h05 (INN) / 2h14 (MUC)</t>
-        </is>
-      </c>
-      <c r="Y36" t="n">
-        <v>360</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>135</v>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>NEEDS VERIFICATION (not individually sourced this pass). Renowned specifically for long-running, high-volume apres-ski (arguably the standout nightlife resort in this database) -- a genuinely distinct positioning. Also has real steep terrain (Harakiri, Austria's steepest marked piste) despite a low, snow-marginal base elevation (630m).</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>j2ski.com, welove2ski.com, inthesnow.com (accessed Aug 2026)</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>30% blue/49% red/21% black per an aggregated piste-map summary (no separate green count found; likely folded into 'blue').</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>Terrain %, lifts, piste km, season and snowfall sourced; ski pass price, accommodation price and 1-5 ratings estimated.</t>
-        </is>
-      </c>
-      <c r="AF36" t="n">
-        <v>47.16667</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>11.86667</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Open-Meteo geocoding API</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Zell am See</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Zell am See-Kaprun</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>757</v>
-      </c>
-      <c r="E37" t="n">
-        <v>3029</v>
-      </c>
-      <c r="F37" t="n">
-        <v>2272</v>
-      </c>
-      <c r="G37" t="n">
-        <v>28</v>
-      </c>
-      <c r="H37" t="n">
-        <v>138</v>
-      </c>
-      <c r="I37" t="n">
-        <v>35</v>
-      </c>
-      <c r="J37" t="n">
-        <v>45</v>
-      </c>
-      <c r="K37" t="n">
-        <v>20</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>sourced</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
-        <v>455</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Yes — Kitzsteinhorn glacier is part of the linked ski area</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Mid Oct–late May (glacier-extended)</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Good — Salzburg has had seasonal direct flights (Sun D'Or) in recent years</t>
-        </is>
-      </c>
-      <c r="R37" t="n">
-        <v>3</v>
-      </c>
-      <c r="S37" t="n">
-        <v>4</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3</v>
-      </c>
-      <c r="U37" t="n">
-        <v>4</v>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Salzburg (SZG) / Munich (MUC)</t>
-        </is>
-      </c>
-      <c r="W37" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>1h16 (SZG) / 2h37 (MUC)</t>
-        </is>
-      </c>
-      <c r="Y37" t="n">
-        <v>370</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>140</v>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>NEEDS VERIFICATION (not individually sourced this pass). Two linked mountains on one pass -- Schmittenhoehe skews intermediate, Kaprun's Maiskogel has a dedicated nursery slope and wide, gentle terrain for families; glacier skiing at Kitzsteinhorn adds snow security most low/mid-elevation Austrian resorts lack. Free connecting ski bus between the two base towns.</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>j2ski.com, powderhounds.com, snowplaza.co.uk (accessed Aug 2026)</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>35% beginner/45% intermediate/20% advanced per an aggregated piste-map summary.</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>Terrain %, elevation, lifts, piste km, season and snowfall sourced; ski pass price, accommodation price and 1-5 ratings estimated.</t>
-        </is>
-      </c>
-      <c r="AF37" t="n">
-        <v>47.32306</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>12.79839</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Open-Meteo geocoding API</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Les Arcs</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Paradiski</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E38" t="n">
-        <v>3226</v>
-      </c>
-      <c r="F38" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G38" t="n">
-        <v>82</v>
-      </c>
-      <c r="H38" t="n">
-        <v>200</v>
-      </c>
-      <c r="I38" t="n">
-        <v>10</v>
-      </c>
-      <c r="J38" t="n">
-        <v>42</v>
-      </c>
-      <c r="K38" t="n">
-        <v>48</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>sourced</t>
-        </is>
-      </c>
-      <c r="M38" t="n">
-        <v>500</v>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Mid Dec–late Apr</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Indirect — via Chambéry/Geneva; no dedicated Israeli charter</t>
-        </is>
-      </c>
-      <c r="R38" t="n">
-        <v>4</v>
-      </c>
-      <c r="S38" t="n">
-        <v>4</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>3</v>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Geneva (GVA) / Chambéry (CMF)</t>
-        </is>
-      </c>
-      <c r="W38" t="n">
-        <v>159.6</v>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>2h33 (GVA) / 1h50 (CMF)</t>
-        </is>
-      </c>
-      <c r="Y38" t="n">
-        <v>368</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>NEEDS VERIFICATION (not individually sourced this pass). Cable-car linked to La Plagne (Paradiski, 425km combined) -- the steepest terrain skew of any resort in this database (48% advanced/expert). High-altitude and snow-secure (summit 3,226m); this is the same Paradiski link that made La Plagne itself come up in the same skideal.co.il research pass, though La Plagne isn't sold as its own package there.</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>wikipedia.org, j2ski.com, skibeat.co.uk, lesarcs-peiseyvallandry.com (accessed Aug 2026)</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>10% beginner/42% intermediate/34% advanced/14% expert per aggregated piste stats; advanced+expert folded together for this database's 3-way schema.</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>Elevation, lifts, piste km, terrain %, season and ski pass price sourced; snowfall, accommodation price and 1-5 ratings estimated. Airport distance has real source disagreement (120-140km). Snowfall ESTIMATED by comparison to Val Thorens (643cm, same general altitude band, already in this database) adjusted down for Les Arcs' lower base elevation -- no direct citation found.</t>
-        </is>
-      </c>
-      <c r="AF38" t="n">
-        <v>45.57755</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>6.78165</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Open-Meteo geocoding API</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Avoriaz</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Portes du Soleil</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E39" t="n">
-        <v>2277</v>
-      </c>
-      <c r="F39" t="n">
-        <v>477</v>
-      </c>
-      <c r="G39" t="n">
-        <v>34</v>
-      </c>
-      <c r="H39" t="n">
-        <v>75</v>
-      </c>
-      <c r="I39" t="n">
-        <v>66</v>
-      </c>
-      <c r="J39" t="n">
-        <v>23</v>
-      </c>
-      <c r="K39" t="n">
-        <v>11</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>sourced</t>
-        </is>
-      </c>
-      <c r="M39" t="n">
-        <v>500</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Mid Dec–mid Apr (typical for the region; not individually confirmed)</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Indirect — via Geneva; no dedicated Israeli charter</t>
-        </is>
-      </c>
-      <c r="R39" t="n">
-        <v>4</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3</v>
-      </c>
-      <c r="U39" t="n">
-        <v>4</v>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Geneva (GVA)</t>
-        </is>
-      </c>
-      <c r="W39" t="n">
-        <v>102.5</v>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>1h39 (GVA)</t>
-        </is>
-      </c>
-      <c r="Y39" t="n">
-        <v>320</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>140</v>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>NEEDS VERIFICATION (not individually sourced this pass). Entirely car-free, built ski-in-ski-out into the mountainside -- a genuinely distinct format from every other resort in this database. Gateway to Portes du Soleil (650km linked), one of the world's largest ski areas, and known for the legendary 'Swiss Wall' and real off-piste/freeride terrain (Lindarets powder fields) despite its family-resort reputation.</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>wikipedia.org, powderhounds.com, alps2alps.com (accessed Aug 2026)</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>7 green + 28 blue + 12 red + 6 black of 53 pistes in Avoriaz's own sector (count-based).</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>Elevation, lifts, piste km and terrain % sourced; ski pass price (Avoriaz has no standalone 6-day product), season end date, snowfall, accommodation price and 1-5 ratings estimated. 6-day ski pass price ESTIMATED: Avoriaz sells passes in 2-day increments, not a 6-day product, and by comparison to similarly-sized French linked areas already in this database. Snowfall ESTIMATED: only a single 'snowiest week' data point (47cm) was found, scaled to a plausible seasonal total -- not a direct annual citation.</t>
-        </is>
-      </c>
-      <c r="AF39" t="n">
-        <v>46.19243</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>6.77341</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Open-Meteo geocoding API</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Les Menuires</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Les Trois Vallées</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>1450</v>
-      </c>
-      <c r="E40" t="n">
-        <v>2850</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G40" t="n">
-        <v>30</v>
-      </c>
-      <c r="H40" t="n">
-        <v>160</v>
-      </c>
-      <c r="I40" t="n">
-        <v>61</v>
-      </c>
-      <c r="J40" t="n">
-        <v>32</v>
-      </c>
-      <c r="K40" t="n">
-        <v>8</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>sourced</t>
-        </is>
-      </c>
-      <c r="M40" t="n">
-        <v>450</v>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Early Dec–mid Apr</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Indirect — via Chambéry/Geneva; no dedicated Israeli charter</t>
-        </is>
-      </c>
-      <c r="R40" t="n">
-        <v>3</v>
-      </c>
-      <c r="S40" t="n">
-        <v>4</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3</v>
-      </c>
-      <c r="U40" t="n">
-        <v>3</v>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Geneva (GVA) / Chambéry (CMF)</t>
-        </is>
-      </c>
-      <c r="W40" t="n">
-        <v>145.6</v>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>2h19 (GVA) / 1h36 (CMF)</t>
-        </is>
-      </c>
-      <c r="Y40" t="n">
-        <v>315</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>NEEDS VERIFICATION (not individually sourced this pass). The value/budget base of Les 3 Vallées -- the same lift network already covered here via Courchevel, Méribel and Val Thorens, giving this database its first cheaper entry point into that circuit. 85% of terrain sits above 1,800m, genuinely snow-secure for its price tier.</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>powderhounds.com, j2ski.com, alps2alps.com (accessed Aug 2026)</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>12 green + 34 blue + 24 red + 6 black of 76 trails (count-based).</t>
-        </is>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>Elevation, lifts, piste km, terrain %, season and ski pass price sourced; snowfall, accommodation price and 1-5 ratings estimated. Snowfall ESTIMATED by comparison to Val Thorens (643cm, same Trois Vallées circuit, already in this database) adjusted down for Les Menuires' lower base elevation -- no direct citation found.</t>
-        </is>
-      </c>
-      <c r="AF40" t="n">
-        <v>45.32293</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>6.53757</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Open-Meteo geocoding API</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Vallnord (Pal-Arinsal)</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Andorra</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Vallnord</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>1550</v>
-      </c>
-      <c r="E41" t="n">
-        <v>2560</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1010</v>
-      </c>
-      <c r="G41" t="n">
-        <v>29</v>
-      </c>
-      <c r="H41" t="n">
-        <v>63</v>
-      </c>
-      <c r="I41" t="n">
-        <v>52</v>
-      </c>
-      <c r="J41" t="n">
-        <v>27</v>
-      </c>
-      <c r="K41" t="n">
-        <v>21</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>sourced</t>
-        </is>
-      </c>
-      <c r="M41" t="n">
-        <v>378</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Early Dec–mid Apr</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Indirect only — via Barcelona/Toulouse with a long onward transfer; no dedicated Israeli charter</t>
-        </is>
-      </c>
-      <c r="R41" t="n">
-        <v>2</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2</v>
-      </c>
-      <c r="U41" t="n">
-        <v>5</v>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Barcelona (BCN)</t>
-        </is>
-      </c>
-      <c r="W41" t="n">
-        <v>215.8</v>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>2h52 (BCN)</t>
-        </is>
-      </c>
-      <c r="Y41" t="n">
-        <v>310</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>NEEDS VERIFICATION (not individually sourced this pass). Andorra's SMALLER, western-side ski area -- genuinely separate from this database's existing Grandvalira entry, not an alternate name for it (confirmed: different mountain, different valley). Explicitly positioned as the most family-oriented resort in the Pyrenees; more compact and relaxed than Grandvalira, gives Andorra a second, cheaper tier in this database.</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>maisonsport.com, arinsal.co.uk, j2ski.com, onthesnow.co.uk (accessed Aug 2026)</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>7 green + 16 blue + 12 red + 9 black of 44 runs (count-based).</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>Elevation, lifts, piste km, terrain %, season, snowfall and airport distance sourced (7-day pass price of EUR357 found, but no clean 6-day figure); accommodation price and 1-5 ratings estimated. 6-day ski pass price ESTIMATED by scaling down from a sourced 7-day adult price of EUR357 (snow-online.com) -- not a direct 6-day citation.</t>
-        </is>
-      </c>
-      <c r="AF41" t="n">
-        <v>42.54499</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.51483</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Open-Meteo geocoding API</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Gudauri</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Georgia</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Greater Caucasus (Kazbegi)</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>1990</v>
-      </c>
-      <c r="E42" t="n">
-        <v>3279</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1289</v>
-      </c>
-      <c r="G42" t="n">
-        <v>20</v>
-      </c>
-      <c r="H42" t="n">
-        <v>76</v>
-      </c>
-      <c r="I42" t="n">
-        <v>30</v>
-      </c>
-      <c r="J42" t="n">
-        <v>50</v>
-      </c>
-      <c r="K42" t="n">
-        <v>20</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>estimated</t>
-        </is>
-      </c>
-      <c r="M42" t="n">
-        <v>350</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>~late Dec–mid Apr (high-altitude, opens ~Dec 27)</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Excellent — Tbilisi (TBS) has direct scheduled TLV service year-round (probed live 2026-08-28: EUR400 Oct / EUR766 Jan round trips priced on Google Flights); one of the largest Israeli ski markets outside Europe</t>
-        </is>
-      </c>
-      <c r="R42" t="n">
-        <v>5</v>
-      </c>
-      <c r="S42" t="n">
-        <v>4</v>
-      </c>
-      <c r="T42" t="n">
-        <v>3</v>
-      </c>
-      <c r="U42" t="n">
-        <v>3</v>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Tbilisi (TBS)</t>
-        </is>
-      </c>
-      <c r="W42" t="n">
-        <v>136.5</v>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>2h35 (TBS)</t>
-        </is>
-      </c>
-      <c r="Y42" t="n">
-        <v>116</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>Highest-value freeride destination in the database: entirely above the tree line, 1,990-3,279m, famous for accessible off-piste and heliskiing; modern Doppelmayr lifts; nightlife modest, resort is purpose-built. 6-day pass 340 GEL (~EUR116). Accommodation figure estimated.</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>skiresort.com, gudauri.com, snow-forecast.com, j2ski.com (accessed Aug 2026)</t>
-        </is>
-      </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>estimated</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>Terrain split estimated from qualitative guides; pass converted from GEL.</t>
-        </is>
-      </c>
-      <c r="AF42" t="n">
-        <v>42.4796</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>44.4805</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Open-Meteo geocoding API</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Sella Ronda (Dolomiti)</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Sella Ronda / Dolomiti Superski</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>1465</v>
-      </c>
-      <c r="E43" t="n">
-        <v>3269</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1804</v>
-      </c>
-      <c r="G43" t="n">
-        <v>450</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I43" t="n">
-        <v>30</v>
-      </c>
-      <c r="J43" t="n">
-        <v>55</v>
-      </c>
-      <c r="K43" t="n">
-        <v>15</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>estimated</t>
-        </is>
-      </c>
-      <c r="M43" t="n">
-        <v>300</v>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Yes (Marmolada)</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>~4 Dec–4 Apr (published 26/27 dates)</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Indirect — via Innsbruck/Verona/Venice; INN and VRN both have priced TLV service (probed live 2026-08-28)</t>
-        </is>
-      </c>
-      <c r="R43" t="n">
-        <v>3</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3</v>
-      </c>
-      <c r="T43" t="n">
-        <v>3</v>
-      </c>
-      <c r="U43" t="n">
-        <v>5</v>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Verona (VRN) / Innsbruck (INN) / Venice Marco Polo (VCE)</t>
-        </is>
-      </c>
-      <c r="W43" t="n">
-        <v>193.4</v>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>2h34 (VRN) / 2h53 (INN) / 2h15 (VCE)</t>
-        </is>
-      </c>
-      <c r="Y43" t="n">
-        <v>357</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>AREA SCOPE, like Grandvalira: the 44km Sella Ronda circuit (23km skied) around the Sella massif linking Selva, Corvara/Colfosco, Arabba and Canazei -- lift/piste figures are the full Dolomiti Superski network (450 lifts / 1,200km) its one pass covers. Overlaps Val Gardena (Selva), which is also in this database as the single-valley entry; this row is the circuit-as-destination the Israeli operators sell. 6-day Dolomiti Superski EUR357 (25/26 published price; 26/27 not yet out).</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>dolomitisuperski.com, val-gardena.com, alta-badia.org, dolomiti.org (accessed Aug 2026)</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>estimated</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>Terrain split estimated; area-scope figures per the note.</t>
-        </is>
-      </c>
-      <c r="AF43" t="n">
-        <v>46.509</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>11.803</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Open-Meteo geocoding API (Passo Gardena area midpoint)</t>
-        </is>
-      </c>
-    </row>
+    <row r="34" ht="70" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:AE2"/>
